--- a/sistema-estudio/Ejemplo Planificador Oposición.xlsx
+++ b/sistema-estudio/Ejemplo Planificador Oposición.xlsx
@@ -32,11 +32,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="mmmm yyyy"/>
-    <numFmt numFmtId="167" formatCode="d"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="mmmm yyyy"/>
+    <numFmt numFmtId="166" formatCode="d"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -462,7 +461,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -521,28 +520,28 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -551,91 +550,91 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -653,10 +652,10 @@
     <xf numFmtId="1" fontId="7" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -665,7 +664,7 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -679,6 +678,111 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,7 +990,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575">
+            <a:ln w="28000">
               <a:solidFill>
                 <a:srgbClr val="38761D"/>
               </a:solidFill>
@@ -901,11 +1005,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <cat>
-            <numRef>
-              <f>'Progreso'!$AP$2:$AP$35</f>
-            </numRef>
-          </cat>
           <val>
             <numRef>
               <f>'Progreso'!$AU$2:$AU$35</f>
@@ -924,7 +1023,7 @@
           <spPr>
             <a:ln w="12700">
               <a:solidFill>
-                <a:srgbClr val="9E9E9E"/>
+                <a:srgbClr val="9AA0A6"/>
               </a:solidFill>
               <a:prstDash val="dash"/>
             </a:ln>
@@ -937,11 +1036,6 @@
               </a:ln>
             </spPr>
           </marker>
-          <cat>
-            <numRef>
-              <f>'Progreso'!$AP$2:$AP$35</f>
-            </numRef>
-          </cat>
           <val>
             <numRef>
               <f>'Progreso'!$AX$2:$AX$35</f>
@@ -963,7 +1057,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="1C4587"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -980,6 +1077,7 @@
               <f>'Progreso'!$AW$2:$AW$35</f>
             </numRef>
           </val>
+          <smooth val="1"/>
         </ser>
         <axId val="10"/>
         <axId val="200"/>
@@ -989,7 +1087,7 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="b"/>
+        <axPos val="l"/>
         <title>
           <tx>
             <rich>
@@ -1032,9 +1130,11 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="max"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -1061,13 +1161,13 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
-        <crosses val="max"/>
       </valAx>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
-    <plotVisOnly val="0"/>
+    <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
 </chartSpace>
@@ -1097,7 +1197,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7920000" cy="3420000"/>
+    <ext cx="8640000" cy="3420000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1191,8 +1291,8 @@
     <tableColumn id="5" name="Semana 28"/>
     <tableColumn id="6" name="Semana 29"/>
     <tableColumn id="7" name="Semana 30"/>
-    <tableColumn id="8" name="-"/>
-    <tableColumn id="9" name="–"/>
+    <tableColumn id="8" name=" "/>
+    <tableColumn id="9" name="  "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1547,7 +1647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A2:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
     <col width="13.57" customWidth="1" min="1" max="1"/>
@@ -1564,7 +1664,6 @@
     <col width="13.57" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="22.5" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2281,12 +2380,12 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t> </t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>–</t>
+          <t>  </t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -2821,42 +2920,42 @@
           <t>Tema 1</t>
         </is>
       </c>
-      <c r="B2" s="20" t="n">
+      <c r="B2" s="73" t="n">
         <v>46174</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="74">
         <f>IF($B2="","",IF(R2&lt;&gt;"",R2,(B2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="75">
         <f>IF($B2="","",IF(S2&lt;&gt;"",S2,(C2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="76">
         <f>IF($B2="","",IF(T2&lt;&gt;"",T2,(D2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="77">
         <f>IF($B2="","",IF(U2&lt;&gt;"",U2,(E2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="78">
         <f>IF($B2="","",IF(V2&lt;&gt;"",V2,(F2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="78">
         <f>IF($B2="","",IF(W2&lt;&gt;"",W2,(G2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="78">
         <f>IF($B2="","",IF(X2&lt;&gt;"",X2,(H2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J2" s="25">
+      <c r="J2" s="78">
         <f>IF($B2="","",IF(Y2&lt;&gt;"",Y2,(I2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K2" s="25">
+      <c r="K2" s="78">
         <f>IF($B2="","",IF(Z2&lt;&gt;"",Z2,(J2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J2+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -2874,13 +2973,13 @@
         <f>IF(COUNTIF(DIAS_ESTUDIO,$O$2)&gt;0,0,IF(COUNTIF(DIAS_ESTUDIO,$O$3)&gt;0,1,IF(COUNTIF(DIAS_ESTUDIO,$O$4)&gt;0,2,IF(COUNTIF(DIAS_ESTUDIO,$O$5)&gt;0,3,IF(COUNTIF(DIAS_ESTUDIO,$O$6)&gt;0,4,IF(COUNTIF(DIAS_ESTUDIO,$O$7)&gt;0,5,IF(COUNTIF(DIAS_ESTUDIO,$O$8)&gt;0,6,0)))))))</f>
         <v/>
       </c>
-      <c r="R2" s="27" t="n">
+      <c r="R2" s="79" t="n">
         <v>46176</v>
       </c>
-      <c r="S2" s="27" t="n">
+      <c r="S2" s="79" t="n">
         <v>46182</v>
       </c>
-      <c r="T2" s="27" t="n">
+      <c r="T2" s="79" t="n">
         <v>46193</v>
       </c>
       <c r="AM2" s="17" t="inlineStr">
@@ -2896,11 +2995,11 @@
       <c r="AP2" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="AQ2" s="27">
+      <c r="AQ2" s="79">
         <f>IF($AN$3="","",$AN$3+(AP2-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR2" s="27">
+      <c r="AR2" s="79">
         <f>IF(AQ2="","",AQ2+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -2971,42 +3070,42 @@
           <t>Tema 2</t>
         </is>
       </c>
-      <c r="B3" s="30" t="n">
+      <c r="B3" s="80" t="n">
         <v>46177</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C3" s="81">
         <f>IF($B3="","",IF(R3&lt;&gt;"",R3,(B3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D3" s="32">
+      <c r="D3" s="82">
         <f>IF($B3="","",IF(S3&lt;&gt;"",S3,(C3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="83">
         <f>IF($B3="","",IF(T3&lt;&gt;"",T3,(D3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="84">
         <f>IF($B3="","",IF(U3&lt;&gt;"",U3,(E3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="85">
         <f>IF($B3="","",IF(V3&lt;&gt;"",V3,(F3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="85">
         <f>IF($B3="","",IF(W3&lt;&gt;"",W3,(G3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I3" s="35">
+      <c r="I3" s="85">
         <f>IF($B3="","",IF(X3&lt;&gt;"",X3,(H3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J3" s="35">
+      <c r="J3" s="85">
         <f>IF($B3="","",IF(Y3&lt;&gt;"",Y3,(I3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K3" s="35">
+      <c r="K3" s="85">
         <f>IF($B3="","",IF(Z3&lt;&gt;"",Z3,(J3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J3+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -3024,13 +3123,13 @@
         <f>IF(COUNTIF(DIAS_ESTUDIO,$O$3)&gt;0,0,IF(COUNTIF(DIAS_ESTUDIO,$O$4)&gt;0,1,IF(COUNTIF(DIAS_ESTUDIO,$O$5)&gt;0,2,IF(COUNTIF(DIAS_ESTUDIO,$O$6)&gt;0,3,IF(COUNTIF(DIAS_ESTUDIO,$O$7)&gt;0,4,IF(COUNTIF(DIAS_ESTUDIO,$O$8)&gt;0,5,IF(COUNTIF(DIAS_ESTUDIO,$O$2)&gt;0,6,0)))))))</f>
         <v/>
       </c>
-      <c r="R3" s="27" t="n">
+      <c r="R3" s="79" t="n">
         <v>46179</v>
       </c>
-      <c r="S3" s="27" t="n">
+      <c r="S3" s="79" t="n">
         <v>46185</v>
       </c>
-      <c r="T3" s="27" t="n">
+      <c r="T3" s="79" t="n">
         <v>46193</v>
       </c>
       <c r="AM3" s="17" t="inlineStr">
@@ -3038,18 +3137,18 @@
           <t>Lunes de la primera sesión</t>
         </is>
       </c>
-      <c r="AN3" s="27">
+      <c r="AN3" s="79">
         <f>IF(MIN($B$2:$K$41)=0,"",MIN($B$2:$K$41)-WEEKDAY(MIN($B$2:$K$41),2)+1)</f>
         <v/>
       </c>
       <c r="AP3" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="AQ3" s="27">
+      <c r="AQ3" s="79">
         <f>IF($AN$3="","",$AN$3+(AP3-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR3" s="27">
+      <c r="AR3" s="79">
         <f>IF(AQ3="","",AQ3+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -3120,42 +3219,42 @@
           <t>Tema 3</t>
         </is>
       </c>
-      <c r="B4" s="36" t="n">
+      <c r="B4" s="86" t="n">
         <v>46179</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="87">
         <f>IF($B4="","",IF(R4&lt;&gt;"",R4,(B4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D4" s="38">
+      <c r="D4" s="88">
         <f>IF($B4="","",IF(S4&lt;&gt;"",S4,(C4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E4" s="38">
+      <c r="E4" s="88">
         <f>IF($B4="","",IF(T4&lt;&gt;"",T4,(D4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="77">
         <f>IF($B4="","",IF(U4&lt;&gt;"",U4,(E4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="78">
         <f>IF($B4="","",IF(V4&lt;&gt;"",V4,(F4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="78">
         <f>IF($B4="","",IF(W4&lt;&gt;"",W4,(G4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="78">
         <f>IF($B4="","",IF(X4&lt;&gt;"",X4,(H4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="78">
         <f>IF($B4="","",IF(Y4&lt;&gt;"",Y4,(I4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="78">
         <f>IF($B4="","",IF(Z4&lt;&gt;"",Z4,(J4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J4+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -3173,13 +3272,13 @@
         <f>IF(COUNTIF(DIAS_ESTUDIO,$O$4)&gt;0,0,IF(COUNTIF(DIAS_ESTUDIO,$O$5)&gt;0,1,IF(COUNTIF(DIAS_ESTUDIO,$O$6)&gt;0,2,IF(COUNTIF(DIAS_ESTUDIO,$O$7)&gt;0,3,IF(COUNTIF(DIAS_ESTUDIO,$O$8)&gt;0,4,IF(COUNTIF(DIAS_ESTUDIO,$O$2)&gt;0,5,IF(COUNTIF(DIAS_ESTUDIO,$O$3)&gt;0,6,0)))))))</f>
         <v/>
       </c>
-      <c r="R4" s="27" t="n">
+      <c r="R4" s="79" t="n">
         <v>46181</v>
       </c>
-      <c r="S4" s="27" t="n">
+      <c r="S4" s="79" t="n">
         <v>46188</v>
       </c>
-      <c r="T4" s="27" t="n">
+      <c r="T4" s="79" t="n">
         <v>46199</v>
       </c>
       <c r="AM4" s="17" t="inlineStr">
@@ -3193,11 +3292,11 @@
       <c r="AP4" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="AQ4" s="27">
+      <c r="AQ4" s="79">
         <f>IF($AN$3="","",$AN$3+(AP4-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR4" s="27">
+      <c r="AR4" s="79">
         <f>IF(AQ4="","",AQ4+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -3272,42 +3371,42 @@
           <t>Tema 4</t>
         </is>
       </c>
-      <c r="B5" s="40" t="n">
+      <c r="B5" s="89" t="n">
         <v>46183</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="90">
         <f>IF($B5="","",IF(R5&lt;&gt;"",R5,(B5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="83">
         <f>IF($B5="","",IF(S5&lt;&gt;"",S5,(C5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="83">
         <f>IF($B5="","",IF(T5&lt;&gt;"",T5,(D5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="84">
         <f>IF($B5="","",IF(U5&lt;&gt;"",U5,(E5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="85">
         <f>IF($B5="","",IF(V5&lt;&gt;"",V5,(F5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H5" s="35">
+      <c r="H5" s="85">
         <f>IF($B5="","",IF(W5&lt;&gt;"",W5,(G5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="85">
         <f>IF($B5="","",IF(X5&lt;&gt;"",X5,(H5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J5" s="35">
+      <c r="J5" s="85">
         <f>IF($B5="","",IF(Y5&lt;&gt;"",Y5,(I5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K5" s="35">
+      <c r="K5" s="85">
         <f>IF($B5="","",IF(Z5&lt;&gt;"",Z5,(J5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J5+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -3325,13 +3424,13 @@
         <f>IF(COUNTIF(DIAS_ESTUDIO,$O$5)&gt;0,0,IF(COUNTIF(DIAS_ESTUDIO,$O$6)&gt;0,1,IF(COUNTIF(DIAS_ESTUDIO,$O$7)&gt;0,2,IF(COUNTIF(DIAS_ESTUDIO,$O$8)&gt;0,3,IF(COUNTIF(DIAS_ESTUDIO,$O$2)&gt;0,4,IF(COUNTIF(DIAS_ESTUDIO,$O$3)&gt;0,5,IF(COUNTIF(DIAS_ESTUDIO,$O$4)&gt;0,6,0)))))))</f>
         <v/>
       </c>
-      <c r="R5" s="27" t="n">
+      <c r="R5" s="79" t="n">
         <v>46186</v>
       </c>
-      <c r="S5" s="27" t="n">
+      <c r="S5" s="79" t="n">
         <v>46193</v>
       </c>
-      <c r="T5" s="27" t="n">
+      <c r="T5" s="79" t="n">
         <v>46200</v>
       </c>
       <c r="AM5" s="17" t="inlineStr">
@@ -3345,11 +3444,11 @@
       <c r="AP5" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="AQ5" s="27">
+      <c r="AQ5" s="79">
         <f>IF($AN$3="","",$AN$3+(AP5-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR5" s="27">
+      <c r="AR5" s="79">
         <f>IF(AQ5="","",AQ5+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -3424,42 +3523,42 @@
           <t>Tema 5</t>
         </is>
       </c>
-      <c r="B6" s="43" t="n">
+      <c r="B6" s="91" t="n">
         <v>46186</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="88">
         <f>IF($B6="","",IF(R6&lt;&gt;"",R6,(B6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="88">
         <f>IF($B6="","",IF(S6&lt;&gt;"",S6,(C6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="92">
         <f>IF($B6="","",IF(T6&lt;&gt;"",T6,(D6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="93">
         <f>IF($B6="","",IF(U6&lt;&gt;"",U6,(E6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="78">
         <f>IF($B6="","",IF(V6&lt;&gt;"",V6,(F6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="78">
         <f>IF($B6="","",IF(W6&lt;&gt;"",W6,(G6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="78">
         <f>IF($B6="","",IF(X6&lt;&gt;"",X6,(H6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="78">
         <f>IF($B6="","",IF(Y6&lt;&gt;"",Y6,(I6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="78">
         <f>IF($B6="","",IF(Z6&lt;&gt;"",Z6,(J6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J6+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -3472,23 +3571,23 @@
         <f>IF(COUNTIF(DIAS_ESTUDIO,$O$6)&gt;0,0,IF(COUNTIF(DIAS_ESTUDIO,$O$7)&gt;0,1,IF(COUNTIF(DIAS_ESTUDIO,$O$8)&gt;0,2,IF(COUNTIF(DIAS_ESTUDIO,$O$2)&gt;0,3,IF(COUNTIF(DIAS_ESTUDIO,$O$3)&gt;0,4,IF(COUNTIF(DIAS_ESTUDIO,$O$4)&gt;0,5,IF(COUNTIF(DIAS_ESTUDIO,$O$5)&gt;0,6,0)))))))</f>
         <v/>
       </c>
-      <c r="R6" s="27" t="n">
+      <c r="R6" s="79" t="n">
         <v>46189</v>
       </c>
-      <c r="S6" s="27" t="n">
+      <c r="S6" s="79" t="n">
         <v>46197</v>
       </c>
-      <c r="T6" s="27" t="n">
+      <c r="T6" s="79" t="n">
         <v>46207</v>
       </c>
       <c r="AP6" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="AQ6" s="27">
+      <c r="AQ6" s="79">
         <f>IF($AN$3="","",$AN$3+(AP6-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR6" s="27">
+      <c r="AR6" s="79">
         <f>IF(AQ6="","",AQ6+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -3563,42 +3662,42 @@
           <t>Tema 6</t>
         </is>
       </c>
-      <c r="B7" s="46" t="n">
+      <c r="B7" s="94" t="n">
         <v>46190</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="90">
         <f>IF($B7="","",IF(R7&lt;&gt;"",R7,(B7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="95">
         <f>IF($B7="","",IF(S7&lt;&gt;"",S7,(C7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="96">
         <f>IF($B7="","",IF(T7&lt;&gt;"",T7,(D7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="85">
         <f>IF($B7="","",IF(U7&lt;&gt;"",U7,(E7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="85">
         <f>IF($B7="","",IF(V7&lt;&gt;"",V7,(F7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="85">
         <f>IF($B7="","",IF(W7&lt;&gt;"",W7,(G7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="85">
         <f>IF($B7="","",IF(X7&lt;&gt;"",X7,(H7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J7" s="35">
+      <c r="J7" s="85">
         <f>IF($B7="","",IF(Y7&lt;&gt;"",Y7,(I7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K7" s="35">
+      <c r="K7" s="85">
         <f>IF($B7="","",IF(Z7&lt;&gt;"",Z7,(J7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J7+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -3611,20 +3710,20 @@
         <f>IF(COUNTIF(DIAS_ESTUDIO,$O$7)&gt;0,0,IF(COUNTIF(DIAS_ESTUDIO,$O$8)&gt;0,1,IF(COUNTIF(DIAS_ESTUDIO,$O$2)&gt;0,2,IF(COUNTIF(DIAS_ESTUDIO,$O$3)&gt;0,3,IF(COUNTIF(DIAS_ESTUDIO,$O$4)&gt;0,4,IF(COUNTIF(DIAS_ESTUDIO,$O$5)&gt;0,5,IF(COUNTIF(DIAS_ESTUDIO,$O$6)&gt;0,6,0)))))))</f>
         <v/>
       </c>
-      <c r="R7" s="27" t="n">
+      <c r="R7" s="79" t="n">
         <v>46192</v>
       </c>
-      <c r="S7" s="27" t="n">
+      <c r="S7" s="79" t="n">
         <v>46200</v>
       </c>
       <c r="AP7" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="AQ7" s="27">
+      <c r="AQ7" s="79">
         <f>IF($AN$3="","",$AN$3+(AP7-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR7" s="27">
+      <c r="AR7" s="79">
         <f>IF(AQ7="","",AQ7+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -3699,42 +3798,42 @@
           <t>Tema 7</t>
         </is>
       </c>
-      <c r="B8" s="49" t="n">
+      <c r="B8" s="97" t="n">
         <v>46195</v>
       </c>
-      <c r="C8" s="50">
+      <c r="C8" s="98">
         <f>IF($B8="","",IF(R8&lt;&gt;"",R8,(B8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="99">
         <f>IF($B8="","",IF(S8&lt;&gt;"",S8,(C8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="77">
         <f>IF($B8="","",IF(T8&lt;&gt;"",T8,(D8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="78">
         <f>IF($B8="","",IF(U8&lt;&gt;"",U8,(E8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="78">
         <f>IF($B8="","",IF(V8&lt;&gt;"",V8,(F8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="78">
         <f>IF($B8="","",IF(W8&lt;&gt;"",W8,(G8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="78">
         <f>IF($B8="","",IF(X8&lt;&gt;"",X8,(H8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="78">
         <f>IF($B8="","",IF(Y8&lt;&gt;"",Y8,(I8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="78">
         <f>IF($B8="","",IF(Z8&lt;&gt;"",Z8,(J8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J8+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -3752,20 +3851,20 @@
         <f>IF(COUNTIF(DIAS_ESTUDIO,$O$8)&gt;0,0,IF(COUNTIF(DIAS_ESTUDIO,$O$2)&gt;0,1,IF(COUNTIF(DIAS_ESTUDIO,$O$3)&gt;0,2,IF(COUNTIF(DIAS_ESTUDIO,$O$4)&gt;0,3,IF(COUNTIF(DIAS_ESTUDIO,$O$5)&gt;0,4,IF(COUNTIF(DIAS_ESTUDIO,$O$6)&gt;0,5,IF(COUNTIF(DIAS_ESTUDIO,$O$7)&gt;0,6,0)))))))</f>
         <v/>
       </c>
-      <c r="R8" s="27" t="n">
+      <c r="R8" s="79" t="n">
         <v>46198</v>
       </c>
-      <c r="S8" s="27" t="n">
+      <c r="S8" s="79" t="n">
         <v>46200</v>
       </c>
       <c r="AP8" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="AQ8" s="27">
+      <c r="AQ8" s="79">
         <f>IF($AN$3="","",$AN$3+(AP8-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR8" s="27">
+      <c r="AR8" s="79">
         <f>IF(AQ8="","",AQ8+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -3840,59 +3939,59 @@
           <t>Tema 8</t>
         </is>
       </c>
-      <c r="B9" s="53" t="n">
+      <c r="B9" s="100" t="n">
         <v>46202</v>
       </c>
-      <c r="C9" s="54">
+      <c r="C9" s="101">
         <f>IF($B9="","",IF(R9&lt;&gt;"",R9,(B9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D9" s="53">
+      <c r="D9" s="100">
         <f>IF($B9="","",IF(S9&lt;&gt;"",S9,(C9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="85">
         <f>IF($B9="","",IF(T9&lt;&gt;"",T9,(D9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="85">
         <f>IF($B9="","",IF(U9&lt;&gt;"",U9,(E9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="85">
         <f>IF($B9="","",IF(V9&lt;&gt;"",V9,(F9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="85">
         <f>IF($B9="","",IF(W9&lt;&gt;"",W9,(G9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="85">
         <f>IF($B9="","",IF(X9&lt;&gt;"",X9,(H9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="85">
         <f>IF($B9="","",IF(Y9&lt;&gt;"",Y9,(I9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K9" s="35">
+      <c r="K9" s="85">
         <f>IF($B9="","",IF(Z9&lt;&gt;"",Z9,(J9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J9+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="M9" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="R9" s="27" t="n">
+      <c r="R9" s="79" t="n">
         <v>46204</v>
       </c>
       <c r="AP9" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="AQ9" s="27">
+      <c r="AQ9" s="79">
         <f>IF($AN$3="","",$AN$3+(AP9-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR9" s="27">
+      <c r="AR9" s="79">
         <f>IF(AQ9="","",AQ9+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -3967,59 +4066,59 @@
           <t>Tema 9</t>
         </is>
       </c>
-      <c r="B10" s="56" t="n">
+      <c r="B10" s="102" t="n">
         <v>46205</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="103">
         <f>IF($B10="","",IF(R10&lt;&gt;"",R10,(B10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="93">
         <f>IF($B10="","",IF(S10&lt;&gt;"",S10,(C10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="78">
         <f>IF($B10="","",IF(T10&lt;&gt;"",T10,(D10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="78">
         <f>IF($B10="","",IF(U10&lt;&gt;"",U10,(E10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="78">
         <f>IF($B10="","",IF(V10&lt;&gt;"",V10,(F10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="78">
         <f>IF($B10="","",IF(W10&lt;&gt;"",W10,(G10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="78">
         <f>IF($B10="","",IF(X10&lt;&gt;"",X10,(H10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="78">
         <f>IF($B10="","",IF(Y10&lt;&gt;"",Y10,(I10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="78">
         <f>IF($B10="","",IF(Z10&lt;&gt;"",Z10,(J10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J10+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="M10" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="R10" s="27" t="n">
+      <c r="R10" s="79" t="n">
         <v>46207</v>
       </c>
       <c r="AP10" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="AQ10" s="27">
+      <c r="AQ10" s="79">
         <f>IF($AN$3="","",$AN$3+(AP10-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR10" s="27">
+      <c r="AR10" s="79">
         <f>IF(AQ10="","",AQ10+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -4094,40 +4193,40 @@
           <t>Tema 10</t>
         </is>
       </c>
-      <c r="B11" s="58" t="n"/>
-      <c r="C11" s="58">
+      <c r="B11" s="104" t="n"/>
+      <c r="C11" s="104">
         <f>IF($B11="","",IF(R11&lt;&gt;"",R11,(B11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="85">
         <f>IF($B11="","",IF(S11&lt;&gt;"",S11,(C11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="85">
         <f>IF($B11="","",IF(T11&lt;&gt;"",T11,(D11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="85">
         <f>IF($B11="","",IF(U11&lt;&gt;"",U11,(E11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="85">
         <f>IF($B11="","",IF(V11&lt;&gt;"",V11,(F11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="85">
         <f>IF($B11="","",IF(W11&lt;&gt;"",W11,(G11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="85">
         <f>IF($B11="","",IF(X11&lt;&gt;"",X11,(H11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="85">
         <f>IF($B11="","",IF(Y11&lt;&gt;"",Y11,(I11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K11" s="35">
+      <c r="K11" s="85">
         <f>IF($B11="","",IF(Z11&lt;&gt;"",Z11,(J11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J11+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -4137,11 +4236,11 @@
       <c r="AP11" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="AQ11" s="27">
+      <c r="AQ11" s="79">
         <f>IF($AN$3="","",$AN$3+(AP11-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR11" s="27">
+      <c r="AR11" s="79">
         <f>IF(AQ11="","",AQ11+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -4216,40 +4315,40 @@
           <t>Tema 11</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25">
+      <c r="B12" s="78" t="n"/>
+      <c r="C12" s="78">
         <f>IF($B12="","",IF(R12&lt;&gt;"",R12,(B12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="78">
         <f>IF($B12="","",IF(S12&lt;&gt;"",S12,(C12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="78">
         <f>IF($B12="","",IF(T12&lt;&gt;"",T12,(D12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="78">
         <f>IF($B12="","",IF(U12&lt;&gt;"",U12,(E12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="78">
         <f>IF($B12="","",IF(V12&lt;&gt;"",V12,(F12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="78">
         <f>IF($B12="","",IF(W12&lt;&gt;"",W12,(G12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="78">
         <f>IF($B12="","",IF(X12&lt;&gt;"",X12,(H12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="78">
         <f>IF($B12="","",IF(Y12&lt;&gt;"",Y12,(I12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="78">
         <f>IF($B12="","",IF(Z12&lt;&gt;"",Z12,(J12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J12+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -4259,11 +4358,11 @@
       <c r="AP12" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="AQ12" s="27">
+      <c r="AQ12" s="79">
         <f>IF($AN$3="","",$AN$3+(AP12-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR12" s="27">
+      <c r="AR12" s="79">
         <f>IF(AQ12="","",AQ12+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -4338,40 +4437,40 @@
           <t>Tema 12</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35">
+      <c r="B13" s="85" t="n"/>
+      <c r="C13" s="85">
         <f>IF($B13="","",IF(R13&lt;&gt;"",R13,(B13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="85">
         <f>IF($B13="","",IF(S13&lt;&gt;"",S13,(C13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="85">
         <f>IF($B13="","",IF(T13&lt;&gt;"",T13,(D13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="85">
         <f>IF($B13="","",IF(U13&lt;&gt;"",U13,(E13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="85">
         <f>IF($B13="","",IF(V13&lt;&gt;"",V13,(F13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H13" s="35">
+      <c r="H13" s="85">
         <f>IF($B13="","",IF(W13&lt;&gt;"",W13,(G13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="85">
         <f>IF($B13="","",IF(X13&lt;&gt;"",X13,(H13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="85">
         <f>IF($B13="","",IF(Y13&lt;&gt;"",Y13,(I13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="85">
         <f>IF($B13="","",IF(Z13&lt;&gt;"",Z13,(J13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J13+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -4381,11 +4480,11 @@
       <c r="AP13" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="AQ13" s="27">
+      <c r="AQ13" s="79">
         <f>IF($AN$3="","",$AN$3+(AP13-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR13" s="27">
+      <c r="AR13" s="79">
         <f>IF(AQ13="","",AQ13+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -4460,40 +4559,40 @@
           <t>Tema 13</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="25">
+      <c r="B14" s="78" t="n"/>
+      <c r="C14" s="78">
         <f>IF($B14="","",IF(R14&lt;&gt;"",R14,(B14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="78">
         <f>IF($B14="","",IF(S14&lt;&gt;"",S14,(C14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="78">
         <f>IF($B14="","",IF(T14&lt;&gt;"",T14,(D14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="78">
         <f>IF($B14="","",IF(U14&lt;&gt;"",U14,(E14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="78">
         <f>IF($B14="","",IF(V14&lt;&gt;"",V14,(F14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="78">
         <f>IF($B14="","",IF(W14&lt;&gt;"",W14,(G14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="78">
         <f>IF($B14="","",IF(X14&lt;&gt;"",X14,(H14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="78">
         <f>IF($B14="","",IF(Y14&lt;&gt;"",Y14,(I14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="78">
         <f>IF($B14="","",IF(Z14&lt;&gt;"",Z14,(J14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J14+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -4503,11 +4602,11 @@
       <c r="AP14" s="26" t="n">
         <v>13</v>
       </c>
-      <c r="AQ14" s="27">
+      <c r="AQ14" s="79">
         <f>IF($AN$3="","",$AN$3+(AP14-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR14" s="27">
+      <c r="AR14" s="79">
         <f>IF(AQ14="","",AQ14+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -4582,40 +4681,40 @@
           <t>Tema 14</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35">
+      <c r="B15" s="85" t="n"/>
+      <c r="C15" s="85">
         <f>IF($B15="","",IF(R15&lt;&gt;"",R15,(B15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="85">
         <f>IF($B15="","",IF(S15&lt;&gt;"",S15,(C15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="85">
         <f>IF($B15="","",IF(T15&lt;&gt;"",T15,(D15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="85">
         <f>IF($B15="","",IF(U15&lt;&gt;"",U15,(E15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G15" s="35">
+      <c r="G15" s="85">
         <f>IF($B15="","",IF(V15&lt;&gt;"",V15,(F15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="85">
         <f>IF($B15="","",IF(W15&lt;&gt;"",W15,(G15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="85">
         <f>IF($B15="","",IF(X15&lt;&gt;"",X15,(H15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="85">
         <f>IF($B15="","",IF(Y15&lt;&gt;"",Y15,(I15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K15" s="35">
+      <c r="K15" s="85">
         <f>IF($B15="","",IF(Z15&lt;&gt;"",Z15,(J15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J15+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -4625,11 +4724,11 @@
       <c r="AP15" s="26" t="n">
         <v>14</v>
       </c>
-      <c r="AQ15" s="27">
+      <c r="AQ15" s="79">
         <f>IF($AN$3="","",$AN$3+(AP15-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR15" s="27">
+      <c r="AR15" s="79">
         <f>IF(AQ15="","",AQ15+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -4704,40 +4803,40 @@
           <t>Tema 15</t>
         </is>
       </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25">
+      <c r="B16" s="78" t="n"/>
+      <c r="C16" s="78">
         <f>IF($B16="","",IF(R16&lt;&gt;"",R16,(B16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="78">
         <f>IF($B16="","",IF(S16&lt;&gt;"",S16,(C16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="78">
         <f>IF($B16="","",IF(T16&lt;&gt;"",T16,(D16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="78">
         <f>IF($B16="","",IF(U16&lt;&gt;"",U16,(E16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="78">
         <f>IF($B16="","",IF(V16&lt;&gt;"",V16,(F16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="78">
         <f>IF($B16="","",IF(W16&lt;&gt;"",W16,(G16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="78">
         <f>IF($B16="","",IF(X16&lt;&gt;"",X16,(H16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="78">
         <f>IF($B16="","",IF(Y16&lt;&gt;"",Y16,(I16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="78">
         <f>IF($B16="","",IF(Z16&lt;&gt;"",Z16,(J16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J16+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -4747,11 +4846,11 @@
       <c r="AP16" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="AQ16" s="27">
+      <c r="AQ16" s="79">
         <f>IF($AN$3="","",$AN$3+(AP16-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR16" s="27">
+      <c r="AR16" s="79">
         <f>IF(AQ16="","",AQ16+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -4826,40 +4925,40 @@
           <t>Tema 16</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35">
+      <c r="B17" s="85" t="n"/>
+      <c r="C17" s="85">
         <f>IF($B17="","",IF(R17&lt;&gt;"",R17,(B17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="85">
         <f>IF($B17="","",IF(S17&lt;&gt;"",S17,(C17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="85">
         <f>IF($B17="","",IF(T17&lt;&gt;"",T17,(D17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="85">
         <f>IF($B17="","",IF(U17&lt;&gt;"",U17,(E17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G17" s="35">
+      <c r="G17" s="85">
         <f>IF($B17="","",IF(V17&lt;&gt;"",V17,(F17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="85">
         <f>IF($B17="","",IF(W17&lt;&gt;"",W17,(G17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="85">
         <f>IF($B17="","",IF(X17&lt;&gt;"",X17,(H17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="85">
         <f>IF($B17="","",IF(Y17&lt;&gt;"",Y17,(I17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K17" s="35">
+      <c r="K17" s="85">
         <f>IF($B17="","",IF(Z17&lt;&gt;"",Z17,(J17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J17+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -4869,11 +4968,11 @@
       <c r="AP17" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="AQ17" s="27">
+      <c r="AQ17" s="79">
         <f>IF($AN$3="","",$AN$3+(AP17-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR17" s="27">
+      <c r="AR17" s="79">
         <f>IF(AQ17="","",AQ17+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -4948,51 +5047,51 @@
           <t>Tema 17</t>
         </is>
       </c>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25">
+      <c r="B18" s="78" t="n"/>
+      <c r="C18" s="78">
         <f>IF($B18="","",IF(R18&lt;&gt;"",R18,(B18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="78">
         <f>IF($B18="","",IF(S18&lt;&gt;"",S18,(C18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="78">
         <f>IF($B18="","",IF(T18&lt;&gt;"",T18,(D18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="78">
         <f>IF($B18="","",IF(U18&lt;&gt;"",U18,(E18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="78">
         <f>IF($B18="","",IF(V18&lt;&gt;"",V18,(F18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="78">
         <f>IF($B18="","",IF(W18&lt;&gt;"",W18,(G18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="78">
         <f>IF($B18="","",IF(X18&lt;&gt;"",X18,(H18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="78">
         <f>IF($B18="","",IF(Y18&lt;&gt;"",Y18,(I18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="78">
         <f>IF($B18="","",IF(Z18&lt;&gt;"",Z18,(J18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J18+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP18" s="26" t="n">
         <v>17</v>
       </c>
-      <c r="AQ18" s="27">
+      <c r="AQ18" s="79">
         <f>IF($AN$3="","",$AN$3+(AP18-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR18" s="27">
+      <c r="AR18" s="79">
         <f>IF(AQ18="","",AQ18+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -5067,51 +5166,51 @@
           <t>Tema 18</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n"/>
-      <c r="C19" s="35">
+      <c r="B19" s="85" t="n"/>
+      <c r="C19" s="85">
         <f>IF($B19="","",IF(R19&lt;&gt;"",R19,(B19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="85">
         <f>IF($B19="","",IF(S19&lt;&gt;"",S19,(C19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="85">
         <f>IF($B19="","",IF(T19&lt;&gt;"",T19,(D19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="85">
         <f>IF($B19="","",IF(U19&lt;&gt;"",U19,(E19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="85">
         <f>IF($B19="","",IF(V19&lt;&gt;"",V19,(F19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="85">
         <f>IF($B19="","",IF(W19&lt;&gt;"",W19,(G19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="85">
         <f>IF($B19="","",IF(X19&lt;&gt;"",X19,(H19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="85">
         <f>IF($B19="","",IF(Y19&lt;&gt;"",Y19,(I19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K19" s="35">
+      <c r="K19" s="85">
         <f>IF($B19="","",IF(Z19&lt;&gt;"",Z19,(J19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J19+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP19" s="26" t="n">
         <v>18</v>
       </c>
-      <c r="AQ19" s="27">
+      <c r="AQ19" s="79">
         <f>IF($AN$3="","",$AN$3+(AP19-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR19" s="27">
+      <c r="AR19" s="79">
         <f>IF(AQ19="","",AQ19+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -5186,51 +5285,51 @@
           <t>Tema 19</t>
         </is>
       </c>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25">
+      <c r="B20" s="78" t="n"/>
+      <c r="C20" s="78">
         <f>IF($B20="","",IF(R20&lt;&gt;"",R20,(B20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="78">
         <f>IF($B20="","",IF(S20&lt;&gt;"",S20,(C20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="78">
         <f>IF($B20="","",IF(T20&lt;&gt;"",T20,(D20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="78">
         <f>IF($B20="","",IF(U20&lt;&gt;"",U20,(E20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="78">
         <f>IF($B20="","",IF(V20&lt;&gt;"",V20,(F20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="78">
         <f>IF($B20="","",IF(W20&lt;&gt;"",W20,(G20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="78">
         <f>IF($B20="","",IF(X20&lt;&gt;"",X20,(H20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="78">
         <f>IF($B20="","",IF(Y20&lt;&gt;"",Y20,(I20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="78">
         <f>IF($B20="","",IF(Z20&lt;&gt;"",Z20,(J20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J20+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP20" s="26" t="n">
         <v>19</v>
       </c>
-      <c r="AQ20" s="27">
+      <c r="AQ20" s="79">
         <f>IF($AN$3="","",$AN$3+(AP20-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR20" s="27">
+      <c r="AR20" s="79">
         <f>IF(AQ20="","",AQ20+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -5305,51 +5404,51 @@
           <t>Tema 20</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n"/>
-      <c r="C21" s="35">
+      <c r="B21" s="85" t="n"/>
+      <c r="C21" s="85">
         <f>IF($B21="","",IF(R21&lt;&gt;"",R21,(B21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="85">
         <f>IF($B21="","",IF(S21&lt;&gt;"",S21,(C21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="85">
         <f>IF($B21="","",IF(T21&lt;&gt;"",T21,(D21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="85">
         <f>IF($B21="","",IF(U21&lt;&gt;"",U21,(E21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="85">
         <f>IF($B21="","",IF(V21&lt;&gt;"",V21,(F21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="85">
         <f>IF($B21="","",IF(W21&lt;&gt;"",W21,(G21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="85">
         <f>IF($B21="","",IF(X21&lt;&gt;"",X21,(H21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="85">
         <f>IF($B21="","",IF(Y21&lt;&gt;"",Y21,(I21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="85">
         <f>IF($B21="","",IF(Z21&lt;&gt;"",Z21,(J21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J21+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP21" s="26" t="n">
         <v>20</v>
       </c>
-      <c r="AQ21" s="27">
+      <c r="AQ21" s="79">
         <f>IF($AN$3="","",$AN$3+(AP21-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR21" s="27">
+      <c r="AR21" s="79">
         <f>IF(AQ21="","",AQ21+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -5424,51 +5523,51 @@
           <t>Tema 21</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="25">
+      <c r="B22" s="78" t="n"/>
+      <c r="C22" s="78">
         <f>IF($B22="","",IF(R22&lt;&gt;"",R22,(B22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="78">
         <f>IF($B22="","",IF(S22&lt;&gt;"",S22,(C22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="78">
         <f>IF($B22="","",IF(T22&lt;&gt;"",T22,(D22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="78">
         <f>IF($B22="","",IF(U22&lt;&gt;"",U22,(E22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="78">
         <f>IF($B22="","",IF(V22&lt;&gt;"",V22,(F22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="78">
         <f>IF($B22="","",IF(W22&lt;&gt;"",W22,(G22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="78">
         <f>IF($B22="","",IF(X22&lt;&gt;"",X22,(H22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="78">
         <f>IF($B22="","",IF(Y22&lt;&gt;"",Y22,(I22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="78">
         <f>IF($B22="","",IF(Z22&lt;&gt;"",Z22,(J22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J22+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP22" s="26" t="n">
         <v>21</v>
       </c>
-      <c r="AQ22" s="27">
+      <c r="AQ22" s="79">
         <f>IF($AN$3="","",$AN$3+(AP22-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR22" s="27">
+      <c r="AR22" s="79">
         <f>IF(AQ22="","",AQ22+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -5543,51 +5642,51 @@
           <t>Tema 22</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35">
+      <c r="B23" s="85" t="n"/>
+      <c r="C23" s="85">
         <f>IF($B23="","",IF(R23&lt;&gt;"",R23,(B23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="85">
         <f>IF($B23="","",IF(S23&lt;&gt;"",S23,(C23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="85">
         <f>IF($B23="","",IF(T23&lt;&gt;"",T23,(D23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="85">
         <f>IF($B23="","",IF(U23&lt;&gt;"",U23,(E23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="85">
         <f>IF($B23="","",IF(V23&lt;&gt;"",V23,(F23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="85">
         <f>IF($B23="","",IF(W23&lt;&gt;"",W23,(G23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="85">
         <f>IF($B23="","",IF(X23&lt;&gt;"",X23,(H23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="85">
         <f>IF($B23="","",IF(Y23&lt;&gt;"",Y23,(I23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K23" s="35">
+      <c r="K23" s="85">
         <f>IF($B23="","",IF(Z23&lt;&gt;"",Z23,(J23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J23+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP23" s="26" t="n">
         <v>22</v>
       </c>
-      <c r="AQ23" s="27">
+      <c r="AQ23" s="79">
         <f>IF($AN$3="","",$AN$3+(AP23-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR23" s="27">
+      <c r="AR23" s="79">
         <f>IF(AQ23="","",AQ23+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -5662,51 +5761,51 @@
           <t>Tema 23</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25">
+      <c r="B24" s="78" t="n"/>
+      <c r="C24" s="78">
         <f>IF($B24="","",IF(R24&lt;&gt;"",R24,(B24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="78">
         <f>IF($B24="","",IF(S24&lt;&gt;"",S24,(C24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="78">
         <f>IF($B24="","",IF(T24&lt;&gt;"",T24,(D24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="78">
         <f>IF($B24="","",IF(U24&lt;&gt;"",U24,(E24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="78">
         <f>IF($B24="","",IF(V24&lt;&gt;"",V24,(F24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="78">
         <f>IF($B24="","",IF(W24&lt;&gt;"",W24,(G24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="78">
         <f>IF($B24="","",IF(X24&lt;&gt;"",X24,(H24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="78">
         <f>IF($B24="","",IF(Y24&lt;&gt;"",Y24,(I24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K24" s="25">
+      <c r="K24" s="78">
         <f>IF($B24="","",IF(Z24&lt;&gt;"",Z24,(J24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J24+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP24" s="26" t="n">
         <v>23</v>
       </c>
-      <c r="AQ24" s="27">
+      <c r="AQ24" s="79">
         <f>IF($AN$3="","",$AN$3+(AP24-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR24" s="27">
+      <c r="AR24" s="79">
         <f>IF(AQ24="","",AQ24+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -5781,51 +5880,51 @@
           <t>Tema 24</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n"/>
-      <c r="C25" s="35">
+      <c r="B25" s="85" t="n"/>
+      <c r="C25" s="85">
         <f>IF($B25="","",IF(R25&lt;&gt;"",R25,(B25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D25" s="35">
+      <c r="D25" s="85">
         <f>IF($B25="","",IF(S25&lt;&gt;"",S25,(C25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="85">
         <f>IF($B25="","",IF(T25&lt;&gt;"",T25,(D25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="85">
         <f>IF($B25="","",IF(U25&lt;&gt;"",U25,(E25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="85">
         <f>IF($B25="","",IF(V25&lt;&gt;"",V25,(F25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="85">
         <f>IF($B25="","",IF(W25&lt;&gt;"",W25,(G25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I25" s="35">
+      <c r="I25" s="85">
         <f>IF($B25="","",IF(X25&lt;&gt;"",X25,(H25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="85">
         <f>IF($B25="","",IF(Y25&lt;&gt;"",Y25,(I25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K25" s="35">
+      <c r="K25" s="85">
         <f>IF($B25="","",IF(Z25&lt;&gt;"",Z25,(J25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J25+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP25" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="AQ25" s="27">
+      <c r="AQ25" s="79">
         <f>IF($AN$3="","",$AN$3+(AP25-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR25" s="27">
+      <c r="AR25" s="79">
         <f>IF(AQ25="","",AQ25+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -5900,51 +5999,51 @@
           <t>Tema 25</t>
         </is>
       </c>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="25">
+      <c r="B26" s="78" t="n"/>
+      <c r="C26" s="78">
         <f>IF($B26="","",IF(R26&lt;&gt;"",R26,(B26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="78">
         <f>IF($B26="","",IF(S26&lt;&gt;"",S26,(C26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="78">
         <f>IF($B26="","",IF(T26&lt;&gt;"",T26,(D26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="78">
         <f>IF($B26="","",IF(U26&lt;&gt;"",U26,(E26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="78">
         <f>IF($B26="","",IF(V26&lt;&gt;"",V26,(F26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="78">
         <f>IF($B26="","",IF(W26&lt;&gt;"",W26,(G26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="78">
         <f>IF($B26="","",IF(X26&lt;&gt;"",X26,(H26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="78">
         <f>IF($B26="","",IF(Y26&lt;&gt;"",Y26,(I26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K26" s="25">
+      <c r="K26" s="78">
         <f>IF($B26="","",IF(Z26&lt;&gt;"",Z26,(J26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J26+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP26" s="26" t="n">
         <v>25</v>
       </c>
-      <c r="AQ26" s="27">
+      <c r="AQ26" s="79">
         <f>IF($AN$3="","",$AN$3+(AP26-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR26" s="27">
+      <c r="AR26" s="79">
         <f>IF(AQ26="","",AQ26+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6019,51 +6118,51 @@
           <t>Tema 26</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n"/>
-      <c r="C27" s="35">
+      <c r="B27" s="85" t="n"/>
+      <c r="C27" s="85">
         <f>IF($B27="","",IF(R27&lt;&gt;"",R27,(B27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D27" s="35">
+      <c r="D27" s="85">
         <f>IF($B27="","",IF(S27&lt;&gt;"",S27,(C27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="85">
         <f>IF($B27="","",IF(T27&lt;&gt;"",T27,(D27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="85">
         <f>IF($B27="","",IF(U27&lt;&gt;"",U27,(E27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="85">
         <f>IF($B27="","",IF(V27&lt;&gt;"",V27,(F27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="85">
         <f>IF($B27="","",IF(W27&lt;&gt;"",W27,(G27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="85">
         <f>IF($B27="","",IF(X27&lt;&gt;"",X27,(H27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="85">
         <f>IF($B27="","",IF(Y27&lt;&gt;"",Y27,(I27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="85">
         <f>IF($B27="","",IF(Z27&lt;&gt;"",Z27,(J27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J27+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP27" s="26" t="n">
         <v>26</v>
       </c>
-      <c r="AQ27" s="27">
+      <c r="AQ27" s="79">
         <f>IF($AN$3="","",$AN$3+(AP27-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR27" s="27">
+      <c r="AR27" s="79">
         <f>IF(AQ27="","",AQ27+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6138,51 +6237,51 @@
           <t>Tema 27</t>
         </is>
       </c>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="25">
+      <c r="B28" s="78" t="n"/>
+      <c r="C28" s="78">
         <f>IF($B28="","",IF(R28&lt;&gt;"",R28,(B28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D28" s="25">
+      <c r="D28" s="78">
         <f>IF($B28="","",IF(S28&lt;&gt;"",S28,(C28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="78">
         <f>IF($B28="","",IF(T28&lt;&gt;"",T28,(D28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="78">
         <f>IF($B28="","",IF(U28&lt;&gt;"",U28,(E28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G28" s="25">
+      <c r="G28" s="78">
         <f>IF($B28="","",IF(V28&lt;&gt;"",V28,(F28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="78">
         <f>IF($B28="","",IF(W28&lt;&gt;"",W28,(G28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="78">
         <f>IF($B28="","",IF(X28&lt;&gt;"",X28,(H28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J28" s="25">
+      <c r="J28" s="78">
         <f>IF($B28="","",IF(Y28&lt;&gt;"",Y28,(I28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="78">
         <f>IF($B28="","",IF(Z28&lt;&gt;"",Z28,(J28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J28+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP28" s="26" t="n">
         <v>27</v>
       </c>
-      <c r="AQ28" s="27">
+      <c r="AQ28" s="79">
         <f>IF($AN$3="","",$AN$3+(AP28-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR28" s="27">
+      <c r="AR28" s="79">
         <f>IF(AQ28="","",AQ28+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6257,51 +6356,51 @@
           <t>Tema 28</t>
         </is>
       </c>
-      <c r="B29" s="35" t="n"/>
-      <c r="C29" s="35">
+      <c r="B29" s="85" t="n"/>
+      <c r="C29" s="85">
         <f>IF($B29="","",IF(R29&lt;&gt;"",R29,(B29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D29" s="35">
+      <c r="D29" s="85">
         <f>IF($B29="","",IF(S29&lt;&gt;"",S29,(C29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E29" s="35">
+      <c r="E29" s="85">
         <f>IF($B29="","",IF(T29&lt;&gt;"",T29,(D29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="85">
         <f>IF($B29="","",IF(U29&lt;&gt;"",U29,(E29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G29" s="35">
+      <c r="G29" s="85">
         <f>IF($B29="","",IF(V29&lt;&gt;"",V29,(F29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H29" s="35">
+      <c r="H29" s="85">
         <f>IF($B29="","",IF(W29&lt;&gt;"",W29,(G29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I29" s="35">
+      <c r="I29" s="85">
         <f>IF($B29="","",IF(X29&lt;&gt;"",X29,(H29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="85">
         <f>IF($B29="","",IF(Y29&lt;&gt;"",Y29,(I29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="85">
         <f>IF($B29="","",IF(Z29&lt;&gt;"",Z29,(J29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J29+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP29" s="26" t="n">
         <v>28</v>
       </c>
-      <c r="AQ29" s="27">
+      <c r="AQ29" s="79">
         <f>IF($AN$3="","",$AN$3+(AP29-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR29" s="27">
+      <c r="AR29" s="79">
         <f>IF(AQ29="","",AQ29+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6376,51 +6475,51 @@
           <t>Tema 29</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25">
+      <c r="B30" s="78" t="n"/>
+      <c r="C30" s="78">
         <f>IF($B30="","",IF(R30&lt;&gt;"",R30,(B30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="78">
         <f>IF($B30="","",IF(S30&lt;&gt;"",S30,(C30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="78">
         <f>IF($B30="","",IF(T30&lt;&gt;"",T30,(D30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="78">
         <f>IF($B30="","",IF(U30&lt;&gt;"",U30,(E30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G30" s="25">
+      <c r="G30" s="78">
         <f>IF($B30="","",IF(V30&lt;&gt;"",V30,(F30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H30" s="25">
+      <c r="H30" s="78">
         <f>IF($B30="","",IF(W30&lt;&gt;"",W30,(G30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="78">
         <f>IF($B30="","",IF(X30&lt;&gt;"",X30,(H30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="78">
         <f>IF($B30="","",IF(Y30&lt;&gt;"",Y30,(I30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K30" s="25">
+      <c r="K30" s="78">
         <f>IF($B30="","",IF(Z30&lt;&gt;"",Z30,(J30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J30+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP30" s="26" t="n">
         <v>29</v>
       </c>
-      <c r="AQ30" s="27">
+      <c r="AQ30" s="79">
         <f>IF($AN$3="","",$AN$3+(AP30-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR30" s="27">
+      <c r="AR30" s="79">
         <f>IF(AQ30="","",AQ30+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6495,51 +6594,51 @@
           <t>Tema 30</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n"/>
-      <c r="C31" s="35">
+      <c r="B31" s="85" t="n"/>
+      <c r="C31" s="85">
         <f>IF($B31="","",IF(R31&lt;&gt;"",R31,(B31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="85">
         <f>IF($B31="","",IF(S31&lt;&gt;"",S31,(C31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="85">
         <f>IF($B31="","",IF(T31&lt;&gt;"",T31,(D31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="85">
         <f>IF($B31="","",IF(U31&lt;&gt;"",U31,(E31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="85">
         <f>IF($B31="","",IF(V31&lt;&gt;"",V31,(F31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="85">
         <f>IF($B31="","",IF(W31&lt;&gt;"",W31,(G31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="85">
         <f>IF($B31="","",IF(X31&lt;&gt;"",X31,(H31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="85">
         <f>IF($B31="","",IF(Y31&lt;&gt;"",Y31,(I31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="85">
         <f>IF($B31="","",IF(Z31&lt;&gt;"",Z31,(J31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J31+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP31" s="26" t="n">
         <v>30</v>
       </c>
-      <c r="AQ31" s="27">
+      <c r="AQ31" s="79">
         <f>IF($AN$3="","",$AN$3+(AP31-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR31" s="27">
+      <c r="AR31" s="79">
         <f>IF(AQ31="","",AQ31+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6614,51 +6713,51 @@
           <t>Tema 31</t>
         </is>
       </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="25">
+      <c r="B32" s="78" t="n"/>
+      <c r="C32" s="78">
         <f>IF($B32="","",IF(R32&lt;&gt;"",R32,(B32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="78">
         <f>IF($B32="","",IF(S32&lt;&gt;"",S32,(C32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="78">
         <f>IF($B32="","",IF(T32&lt;&gt;"",T32,(D32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="78">
         <f>IF($B32="","",IF(U32&lt;&gt;"",U32,(E32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="78">
         <f>IF($B32="","",IF(V32&lt;&gt;"",V32,(F32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="78">
         <f>IF($B32="","",IF(W32&lt;&gt;"",W32,(G32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="78">
         <f>IF($B32="","",IF(X32&lt;&gt;"",X32,(H32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="78">
         <f>IF($B32="","",IF(Y32&lt;&gt;"",Y32,(I32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K32" s="25">
+      <c r="K32" s="78">
         <f>IF($B32="","",IF(Z32&lt;&gt;"",Z32,(J32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J32+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP32" s="26" t="n">
         <v>31</v>
       </c>
-      <c r="AQ32" s="27">
+      <c r="AQ32" s="79">
         <f>IF($AN$3="","",$AN$3+(AP32-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR32" s="27">
+      <c r="AR32" s="79">
         <f>IF(AQ32="","",AQ32+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6733,51 +6832,51 @@
           <t>Tema 32</t>
         </is>
       </c>
-      <c r="B33" s="35" t="n"/>
-      <c r="C33" s="35">
+      <c r="B33" s="85" t="n"/>
+      <c r="C33" s="85">
         <f>IF($B33="","",IF(R33&lt;&gt;"",R33,(B33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="85">
         <f>IF($B33="","",IF(S33&lt;&gt;"",S33,(C33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="85">
         <f>IF($B33="","",IF(T33&lt;&gt;"",T33,(D33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="85">
         <f>IF($B33="","",IF(U33&lt;&gt;"",U33,(E33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="85">
         <f>IF($B33="","",IF(V33&lt;&gt;"",V33,(F33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="85">
         <f>IF($B33="","",IF(W33&lt;&gt;"",W33,(G33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="85">
         <f>IF($B33="","",IF(X33&lt;&gt;"",X33,(H33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="85">
         <f>IF($B33="","",IF(Y33&lt;&gt;"",Y33,(I33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="85">
         <f>IF($B33="","",IF(Z33&lt;&gt;"",Z33,(J33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J33+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP33" s="26" t="n">
         <v>32</v>
       </c>
-      <c r="AQ33" s="27">
+      <c r="AQ33" s="79">
         <f>IF($AN$3="","",$AN$3+(AP33-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR33" s="27">
+      <c r="AR33" s="79">
         <f>IF(AQ33="","",AQ33+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6852,51 +6951,51 @@
           <t>Tema 33</t>
         </is>
       </c>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="25">
+      <c r="B34" s="78" t="n"/>
+      <c r="C34" s="78">
         <f>IF($B34="","",IF(R34&lt;&gt;"",R34,(B34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="78">
         <f>IF($B34="","",IF(S34&lt;&gt;"",S34,(C34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="78">
         <f>IF($B34="","",IF(T34&lt;&gt;"",T34,(D34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="78">
         <f>IF($B34="","",IF(U34&lt;&gt;"",U34,(E34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="78">
         <f>IF($B34="","",IF(V34&lt;&gt;"",V34,(F34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H34" s="25">
+      <c r="H34" s="78">
         <f>IF($B34="","",IF(W34&lt;&gt;"",W34,(G34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I34" s="25">
+      <c r="I34" s="78">
         <f>IF($B34="","",IF(X34&lt;&gt;"",X34,(H34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J34" s="25">
+      <c r="J34" s="78">
         <f>IF($B34="","",IF(Y34&lt;&gt;"",Y34,(I34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K34" s="25">
+      <c r="K34" s="78">
         <f>IF($B34="","",IF(Z34&lt;&gt;"",Z34,(J34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J34+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP34" s="26" t="n">
         <v>33</v>
       </c>
-      <c r="AQ34" s="27">
+      <c r="AQ34" s="79">
         <f>IF($AN$3="","",$AN$3+(AP34-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR34" s="27">
+      <c r="AR34" s="79">
         <f>IF(AQ34="","",AQ34+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -6971,51 +7070,51 @@
           <t>Tema 34</t>
         </is>
       </c>
-      <c r="B35" s="35" t="n"/>
-      <c r="C35" s="35">
+      <c r="B35" s="85" t="n"/>
+      <c r="C35" s="85">
         <f>IF($B35="","",IF(R35&lt;&gt;"",R35,(B35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="85">
         <f>IF($B35="","",IF(S35&lt;&gt;"",S35,(C35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="85">
         <f>IF($B35="","",IF(T35&lt;&gt;"",T35,(D35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="85">
         <f>IF($B35="","",IF(U35&lt;&gt;"",U35,(E35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="85">
         <f>IF($B35="","",IF(V35&lt;&gt;"",V35,(F35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="85">
         <f>IF($B35="","",IF(W35&lt;&gt;"",W35,(G35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="85">
         <f>IF($B35="","",IF(X35&lt;&gt;"",X35,(H35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="85">
         <f>IF($B35="","",IF(Y35&lt;&gt;"",Y35,(I35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="85">
         <f>IF($B35="","",IF(Z35&lt;&gt;"",Z35,(J35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J35+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
       <c r="AP35" s="26" t="n">
         <v>34</v>
       </c>
-      <c r="AQ35" s="27">
+      <c r="AQ35" s="79">
         <f>IF($AN$3="","",$AN$3+(AP35-1)*DIAS_POR_SEMANA)</f>
         <v/>
       </c>
-      <c r="AR35" s="27">
+      <c r="AR35" s="79">
         <f>IF(AQ35="","",AQ35+DIAS_POR_SEMANA-1)</f>
         <v/>
       </c>
@@ -7090,40 +7189,40 @@
           <t>Tema 35</t>
         </is>
       </c>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="25">
+      <c r="B36" s="78" t="n"/>
+      <c r="C36" s="78">
         <f>IF($B36="","",IF(R36&lt;&gt;"",R36,(B36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="78">
         <f>IF($B36="","",IF(S36&lt;&gt;"",S36,(C36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="78">
         <f>IF($B36="","",IF(T36&lt;&gt;"",T36,(D36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="78">
         <f>IF($B36="","",IF(U36&lt;&gt;"",U36,(E36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="78">
         <f>IF($B36="","",IF(V36&lt;&gt;"",V36,(F36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H36" s="25">
+      <c r="H36" s="78">
         <f>IF($B36="","",IF(W36&lt;&gt;"",W36,(G36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I36" s="25">
+      <c r="I36" s="78">
         <f>IF($B36="","",IF(X36&lt;&gt;"",X36,(H36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J36" s="25">
+      <c r="J36" s="78">
         <f>IF($B36="","",IF(Y36&lt;&gt;"",Y36,(I36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="78">
         <f>IF($B36="","",IF(Z36&lt;&gt;"",Z36,(J36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J36+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -7174,40 +7273,40 @@
           <t>Tema 36</t>
         </is>
       </c>
-      <c r="B37" s="35" t="n"/>
-      <c r="C37" s="35">
+      <c r="B37" s="85" t="n"/>
+      <c r="C37" s="85">
         <f>IF($B37="","",IF(R37&lt;&gt;"",R37,(B37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D37" s="35">
+      <c r="D37" s="85">
         <f>IF($B37="","",IF(S37&lt;&gt;"",S37,(C37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E37" s="35">
+      <c r="E37" s="85">
         <f>IF($B37="","",IF(T37&lt;&gt;"",T37,(D37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F37" s="35">
+      <c r="F37" s="85">
         <f>IF($B37="","",IF(U37&lt;&gt;"",U37,(E37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="85">
         <f>IF($B37="","",IF(V37&lt;&gt;"",V37,(F37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H37" s="35">
+      <c r="H37" s="85">
         <f>IF($B37="","",IF(W37&lt;&gt;"",W37,(G37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I37" s="35">
+      <c r="I37" s="85">
         <f>IF($B37="","",IF(X37&lt;&gt;"",X37,(H37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="85">
         <f>IF($B37="","",IF(Y37&lt;&gt;"",Y37,(I37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K37" s="35">
+      <c r="K37" s="85">
         <f>IF($B37="","",IF(Z37&lt;&gt;"",Z37,(J37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J37+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -7258,40 +7357,40 @@
           <t>Tema 37</t>
         </is>
       </c>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="25">
+      <c r="B38" s="78" t="n"/>
+      <c r="C38" s="78">
         <f>IF($B38="","",IF(R38&lt;&gt;"",R38,(B38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D38" s="25">
+      <c r="D38" s="78">
         <f>IF($B38="","",IF(S38&lt;&gt;"",S38,(C38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E38" s="25">
+      <c r="E38" s="78">
         <f>IF($B38="","",IF(T38&lt;&gt;"",T38,(D38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F38" s="25">
+      <c r="F38" s="78">
         <f>IF($B38="","",IF(U38&lt;&gt;"",U38,(E38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G38" s="25">
+      <c r="G38" s="78">
         <f>IF($B38="","",IF(V38&lt;&gt;"",V38,(F38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H38" s="25">
+      <c r="H38" s="78">
         <f>IF($B38="","",IF(W38&lt;&gt;"",W38,(G38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I38" s="25">
+      <c r="I38" s="78">
         <f>IF($B38="","",IF(X38&lt;&gt;"",X38,(H38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J38" s="25">
+      <c r="J38" s="78">
         <f>IF($B38="","",IF(Y38&lt;&gt;"",Y38,(I38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K38" s="25">
+      <c r="K38" s="78">
         <f>IF($B38="","",IF(Z38&lt;&gt;"",Z38,(J38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J38+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -7342,40 +7441,40 @@
           <t>Tema 38</t>
         </is>
       </c>
-      <c r="B39" s="35" t="n"/>
-      <c r="C39" s="35">
+      <c r="B39" s="85" t="n"/>
+      <c r="C39" s="85">
         <f>IF($B39="","",IF(R39&lt;&gt;"",R39,(B39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="85">
         <f>IF($B39="","",IF(S39&lt;&gt;"",S39,(C39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="85">
         <f>IF($B39="","",IF(T39&lt;&gt;"",T39,(D39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="85">
         <f>IF($B39="","",IF(U39&lt;&gt;"",U39,(E39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G39" s="35">
+      <c r="G39" s="85">
         <f>IF($B39="","",IF(V39&lt;&gt;"",V39,(F39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H39" s="35">
+      <c r="H39" s="85">
         <f>IF($B39="","",IF(W39&lt;&gt;"",W39,(G39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="85">
         <f>IF($B39="","",IF(X39&lt;&gt;"",X39,(H39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="85">
         <f>IF($B39="","",IF(Y39&lt;&gt;"",Y39,(I39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K39" s="35">
+      <c r="K39" s="85">
         <f>IF($B39="","",IF(Z39&lt;&gt;"",Z39,(J39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J39+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -7426,40 +7525,40 @@
           <t>Tema 39</t>
         </is>
       </c>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="25">
+      <c r="B40" s="78" t="n"/>
+      <c r="C40" s="78">
         <f>IF($B40="","",IF(R40&lt;&gt;"",R40,(B40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D40" s="25">
+      <c r="D40" s="78">
         <f>IF($B40="","",IF(S40&lt;&gt;"",S40,(C40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="78">
         <f>IF($B40="","",IF(T40&lt;&gt;"",T40,(D40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F40" s="25">
+      <c r="F40" s="78">
         <f>IF($B40="","",IF(U40&lt;&gt;"",U40,(E40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G40" s="25">
+      <c r="G40" s="78">
         <f>IF($B40="","",IF(V40&lt;&gt;"",V40,(F40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H40" s="25">
+      <c r="H40" s="78">
         <f>IF($B40="","",IF(W40&lt;&gt;"",W40,(G40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I40" s="25">
+      <c r="I40" s="78">
         <f>IF($B40="","",IF(X40&lt;&gt;"",X40,(H40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J40" s="25">
+      <c r="J40" s="78">
         <f>IF($B40="","",IF(Y40&lt;&gt;"",Y40,(I40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="78">
         <f>IF($B40="","",IF(Z40&lt;&gt;"",Z40,(J40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J40+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -7510,40 +7609,40 @@
           <t>Tema 40</t>
         </is>
       </c>
-      <c r="B41" s="35" t="n"/>
-      <c r="C41" s="35">
+      <c r="B41" s="85" t="n"/>
+      <c r="C41" s="85">
         <f>IF($B41="","",IF(R41&lt;&gt;"",R41,(B41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(B41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="D41" s="35">
+      <c r="D41" s="85">
         <f>IF($B41="","",IF(S41&lt;&gt;"",S41,(C41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(C41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="85">
         <f>IF($B41="","",IF(T41&lt;&gt;"",T41,(D41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(D41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="85">
         <f>IF($B41="","",IF(U41&lt;&gt;"",U41,(E41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(E41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="G41" s="35">
+      <c r="G41" s="85">
         <f>IF($B41="","",IF(V41&lt;&gt;"",V41,(F41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(F41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="H41" s="35">
+      <c r="H41" s="85">
         <f>IF($B41="","",IF(W41&lt;&gt;"",W41,(G41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(G41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="I41" s="35">
+      <c r="I41" s="85">
         <f>IF($B41="","",IF(X41&lt;&gt;"",X41,(H41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(H41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="85">
         <f>IF($B41="","",IF(Y41&lt;&gt;"",Y41,(I41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(I41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
-      <c r="K41" s="35">
+      <c r="K41" s="85">
         <f>IF($B41="","",IF(Z41&lt;&gt;"",Z41,(J41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)))+INDEX(DESPLAZAMIENTO,WEEKDAY(J41+INDEX(INTERVALOS,COLUMN()-COLUMN($B$1)),2))))</f>
         <v/>
       </c>
@@ -7735,11 +7834,11 @@
           <t>Hoy</t>
         </is>
       </c>
-      <c r="B2" s="64">
+      <c r="B2" s="105">
         <f>TODAY()</f>
         <v/>
       </c>
-      <c r="G2" s="65">
+      <c r="G2" s="106">
         <f>DATE(YEAR(HOY),MONTH(HOY),1)</f>
         <v/>
       </c>
@@ -7864,31 +7963,31 @@
         <f>SUMPRODUCT((Progreso!$AZ$2:$BI$41&gt;$B$2)*(Progreso!$AZ$2:$BI$41&lt;=$B$2+VENTANA_PROXIMA))</f>
         <v/>
       </c>
-      <c r="G5" s="68">
+      <c r="G5" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="H5" s="68">
+      <c r="H5" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="I5" s="68">
+      <c r="I5" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="J5" s="68">
+      <c r="J5" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="K5" s="68">
+      <c r="K5" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="L5" s="68">
+      <c r="L5" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="M5" s="68">
+      <c r="M5" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
@@ -7912,31 +8011,31 @@
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="G6" s="68">
+      <c r="G6" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="H6" s="68">
+      <c r="H6" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="I6" s="68">
+      <c r="I6" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="J6" s="68">
+      <c r="J6" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="K6" s="68">
+      <c r="K6" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="L6" s="68">
+      <c r="L6" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="M6" s="68">
+      <c r="M6" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
@@ -7960,31 +8059,31 @@
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="G7" s="68">
+      <c r="G7" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="H7" s="68">
+      <c r="H7" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
@@ -8008,31 +8107,31 @@
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="G8" s="68">
+      <c r="G8" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="H8" s="68">
+      <c r="H8" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="I8" s="68">
+      <c r="I8" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="J8" s="68">
+      <c r="J8" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="K8" s="68">
+      <c r="K8" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="L8" s="68">
+      <c r="L8" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="M8" s="68">
+      <c r="M8" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
@@ -8056,31 +8155,31 @@
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="G9" s="68">
+      <c r="G9" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="H9" s="68">
+      <c r="H9" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="I9" s="68">
+      <c r="I9" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="J9" s="68">
+      <c r="J9" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="K9" s="68">
+      <c r="K9" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="L9" s="68">
+      <c r="L9" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="M9" s="68">
+      <c r="M9" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
@@ -8104,31 +8203,31 @@
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="G10" s="68">
+      <c r="G10" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="H10" s="68">
+      <c r="H10" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="I10" s="68">
+      <c r="I10" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="J10" s="68">
+      <c r="J10" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="K10" s="68">
+      <c r="K10" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="L10" s="68">
+      <c r="L10" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
-      <c r="M10" s="68">
+      <c r="M10" s="107">
         <f>IF(MONTH($G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))&lt;&gt;MONTH($G$2),"",$G$2-WEEKDAY($G$2,2)+1+(ROW()-ROW($G$3)-2)*DIAS_POR_SEMANA+(COLUMN()-COLUMN($G$3)))</f>
         <v/>
       </c>
@@ -8222,7 +8321,7 @@
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="25">
+      <c r="A13" s="78">
         <f>IF($V13="","",INDEX($R$2:$R$401,$V13))</f>
         <v/>
       </c>
@@ -8266,7 +8365,7 @@
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="35">
+      <c r="A14" s="85">
         <f>IF($V14="","",INDEX($R$2:$R$401,$V14))</f>
         <v/>
       </c>
@@ -8310,7 +8409,7 @@
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="25">
+      <c r="A15" s="78">
         <f>IF($V15="","",INDEX($R$2:$R$401,$V15))</f>
         <v/>
       </c>
@@ -8354,7 +8453,7 @@
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="35">
+      <c r="A16" s="85">
         <f>IF($V16="","",INDEX($R$2:$R$401,$V16))</f>
         <v/>
       </c>
@@ -8398,7 +8497,7 @@
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="25">
+      <c r="A17" s="78">
         <f>IF($V17="","",INDEX($R$2:$R$401,$V17))</f>
         <v/>
       </c>
@@ -8442,7 +8541,7 @@
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="35">
+      <c r="A18" s="85">
         <f>IF($V18="","",INDEX($R$2:$R$401,$V18))</f>
         <v/>
       </c>
@@ -8486,7 +8585,7 @@
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="25">
+      <c r="A19" s="78">
         <f>IF($V19="","",INDEX($R$2:$R$401,$V19))</f>
         <v/>
       </c>
@@ -8530,7 +8629,7 @@
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="35">
+      <c r="A20" s="85">
         <f>IF($V20="","",INDEX($R$2:$R$401,$V20))</f>
         <v/>
       </c>
@@ -8574,7 +8673,7 @@
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="25">
+      <c r="A21" s="78">
         <f>IF($V21="","",INDEX($R$2:$R$401,$V21))</f>
         <v/>
       </c>
@@ -8618,7 +8717,7 @@
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="35">
+      <c r="A22" s="85">
         <f>IF($V22="","",INDEX($R$2:$R$401,$V22))</f>
         <v/>
       </c>
@@ -8662,7 +8761,7 @@
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="25">
+      <c r="A23" s="78">
         <f>IF($V23="","",INDEX($R$2:$R$401,$V23))</f>
         <v/>
       </c>
@@ -8706,7 +8805,7 @@
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="35">
+      <c r="A24" s="85">
         <f>IF($V24="","",INDEX($R$2:$R$401,$V24))</f>
         <v/>
       </c>
@@ -8750,7 +8849,7 @@
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="25">
+      <c r="A25" s="78">
         <f>IF($V25="","",INDEX($R$2:$R$401,$V25))</f>
         <v/>
       </c>
@@ -8794,7 +8893,7 @@
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="35">
+      <c r="A26" s="85">
         <f>IF($V26="","",INDEX($R$2:$R$401,$V26))</f>
         <v/>
       </c>
@@ -8838,7 +8937,7 @@
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="25">
+      <c r="A27" s="78">
         <f>IF($V27="","",INDEX($R$2:$R$401,$V27))</f>
         <v/>
       </c>
@@ -8882,7 +8981,7 @@
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="35">
+      <c r="A28" s="85">
         <f>IF($V28="","",INDEX($R$2:$R$401,$V28))</f>
         <v/>
       </c>
@@ -8926,7 +9025,7 @@
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="25">
+      <c r="A29" s="78">
         <f>IF($V29="","",INDEX($R$2:$R$401,$V29))</f>
         <v/>
       </c>
@@ -8970,7 +9069,7 @@
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="35">
+      <c r="A30" s="85">
         <f>IF($V30="","",INDEX($R$2:$R$401,$V30))</f>
         <v/>
       </c>
@@ -9014,7 +9113,7 @@
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="25">
+      <c r="A31" s="78">
         <f>IF($V31="","",INDEX($R$2:$R$401,$V31))</f>
         <v/>
       </c>
@@ -9058,7 +9157,7 @@
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="35">
+      <c r="A32" s="85">
         <f>IF($V32="","",INDEX($R$2:$R$401,$V32))</f>
         <v/>
       </c>
@@ -9102,7 +9201,7 @@
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="25">
+      <c r="A33" s="78">
         <f>IF($V33="","",INDEX($R$2:$R$401,$V33))</f>
         <v/>
       </c>
@@ -9146,7 +9245,7 @@
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="35">
+      <c r="A34" s="85">
         <f>IF($V34="","",INDEX($R$2:$R$401,$V34))</f>
         <v/>
       </c>
@@ -9190,7 +9289,7 @@
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="25">
+      <c r="A35" s="78">
         <f>IF($V35="","",INDEX($R$2:$R$401,$V35))</f>
         <v/>
       </c>
@@ -9234,7 +9333,7 @@
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="35">
+      <c r="A36" s="85">
         <f>IF($V36="","",INDEX($R$2:$R$401,$V36))</f>
         <v/>
       </c>
@@ -9278,7 +9377,7 @@
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="25">
+      <c r="A37" s="78">
         <f>IF($V37="","",INDEX($R$2:$R$401,$V37))</f>
         <v/>
       </c>
@@ -9322,7 +9421,7 @@
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="35">
+      <c r="A38" s="85">
         <f>IF($V38="","",INDEX($R$2:$R$401,$V38))</f>
         <v/>
       </c>
@@ -9366,7 +9465,7 @@
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="25">
+      <c r="A39" s="78">
         <f>IF($V39="","",INDEX($R$2:$R$401,$V39))</f>
         <v/>
       </c>
@@ -9410,7 +9509,7 @@
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="35">
+      <c r="A40" s="85">
         <f>IF($V40="","",INDEX($R$2:$R$401,$V40))</f>
         <v/>
       </c>
@@ -9454,7 +9553,7 @@
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="25">
+      <c r="A41" s="78">
         <f>IF($V41="","",INDEX($R$2:$R$401,$V41))</f>
         <v/>
       </c>
@@ -9498,7 +9597,7 @@
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="35">
+      <c r="A42" s="85">
         <f>IF($V42="","",INDEX($R$2:$R$401,$V42))</f>
         <v/>
       </c>
@@ -9542,7 +9641,7 @@
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="25">
+      <c r="A43" s="78">
         <f>IF($V43="","",INDEX($R$2:$R$401,$V43))</f>
         <v/>
       </c>
@@ -9586,7 +9685,7 @@
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="35">
+      <c r="A44" s="85">
         <f>IF($V44="","",INDEX($R$2:$R$401,$V44))</f>
         <v/>
       </c>
@@ -9630,7 +9729,7 @@
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="25">
+      <c r="A45" s="78">
         <f>IF($V45="","",INDEX($R$2:$R$401,$V45))</f>
         <v/>
       </c>
@@ -9674,7 +9773,7 @@
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="35">
+      <c r="A46" s="85">
         <f>IF($V46="","",INDEX($R$2:$R$401,$V46))</f>
         <v/>
       </c>
@@ -9718,7 +9817,7 @@
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="25">
+      <c r="A47" s="78">
         <f>IF($V47="","",INDEX($R$2:$R$401,$V47))</f>
         <v/>
       </c>
@@ -9762,7 +9861,7 @@
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="35">
+      <c r="A48" s="85">
         <f>IF($V48="","",INDEX($R$2:$R$401,$V48))</f>
         <v/>
       </c>
@@ -9806,7 +9905,7 @@
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="25">
+      <c r="A49" s="78">
         <f>IF($V49="","",INDEX($R$2:$R$401,$V49))</f>
         <v/>
       </c>
@@ -9850,7 +9949,7 @@
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="35">
+      <c r="A50" s="85">
         <f>IF($V50="","",INDEX($R$2:$R$401,$V50))</f>
         <v/>
       </c>
@@ -9894,7 +9993,7 @@
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="25">
+      <c r="A51" s="78">
         <f>IF($V51="","",INDEX($R$2:$R$401,$V51))</f>
         <v/>
       </c>
@@ -9938,7 +10037,7 @@
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="35">
+      <c r="A52" s="85">
         <f>IF($V52="","",INDEX($R$2:$R$401,$V52))</f>
         <v/>
       </c>
@@ -9982,7 +10081,7 @@
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="25">
+      <c r="A53" s="78">
         <f>IF($V53="","",INDEX($R$2:$R$401,$V53))</f>
         <v/>
       </c>
@@ -10026,7 +10125,7 @@
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="35">
+      <c r="A54" s="85">
         <f>IF($V54="","",INDEX($R$2:$R$401,$V54))</f>
         <v/>
       </c>
@@ -10070,7 +10169,7 @@
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="25">
+      <c r="A55" s="78">
         <f>IF($V55="","",INDEX($R$2:$R$401,$V55))</f>
         <v/>
       </c>
@@ -10114,7 +10213,7 @@
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="35">
+      <c r="A56" s="85">
         <f>IF($V56="","",INDEX($R$2:$R$401,$V56))</f>
         <v/>
       </c>
@@ -10158,7 +10257,7 @@
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="25">
+      <c r="A57" s="78">
         <f>IF($V57="","",INDEX($R$2:$R$401,$V57))</f>
         <v/>
       </c>
@@ -10202,7 +10301,7 @@
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="35">
+      <c r="A58" s="85">
         <f>IF($V58="","",INDEX($R$2:$R$401,$V58))</f>
         <v/>
       </c>
@@ -10246,7 +10345,7 @@
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="25">
+      <c r="A59" s="78">
         <f>IF($V59="","",INDEX($R$2:$R$401,$V59))</f>
         <v/>
       </c>
@@ -10290,7 +10389,7 @@
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="35">
+      <c r="A60" s="85">
         <f>IF($V60="","",INDEX($R$2:$R$401,$V60))</f>
         <v/>
       </c>
@@ -10334,7 +10433,7 @@
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" s="25">
+      <c r="A61" s="78">
         <f>IF($V61="","",INDEX($R$2:$R$401,$V61))</f>
         <v/>
       </c>
@@ -10378,7 +10477,7 @@
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="35">
+      <c r="A62" s="85">
         <f>IF($V62="","",INDEX($R$2:$R$401,$V62))</f>
         <v/>
       </c>
@@ -10422,7 +10521,7 @@
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="25">
+      <c r="A63" s="78">
         <f>IF($V63="","",INDEX($R$2:$R$401,$V63))</f>
         <v/>
       </c>
@@ -10466,7 +10565,7 @@
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="35">
+      <c r="A64" s="85">
         <f>IF($V64="","",INDEX($R$2:$R$401,$V64))</f>
         <v/>
       </c>
@@ -10510,7 +10609,7 @@
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" s="25">
+      <c r="A65" s="78">
         <f>IF($V65="","",INDEX($R$2:$R$401,$V65))</f>
         <v/>
       </c>
@@ -10554,7 +10653,7 @@
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
-      <c r="A66" s="35">
+      <c r="A66" s="85">
         <f>IF($V66="","",INDEX($R$2:$R$401,$V66))</f>
         <v/>
       </c>
@@ -10598,7 +10697,7 @@
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
-      <c r="A67" s="25">
+      <c r="A67" s="78">
         <f>IF($V67="","",INDEX($R$2:$R$401,$V67))</f>
         <v/>
       </c>
@@ -10642,7 +10741,7 @@
       </c>
     </row>
     <row r="68" ht="22.5" customHeight="1">
-      <c r="A68" s="35">
+      <c r="A68" s="85">
         <f>IF($V68="","",INDEX($R$2:$R$401,$V68))</f>
         <v/>
       </c>
@@ -10686,7 +10785,7 @@
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
-      <c r="A69" s="25">
+      <c r="A69" s="78">
         <f>IF($V69="","",INDEX($R$2:$R$401,$V69))</f>
         <v/>
       </c>
@@ -10730,7 +10829,7 @@
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
-      <c r="A70" s="35">
+      <c r="A70" s="85">
         <f>IF($V70="","",INDEX($R$2:$R$401,$V70))</f>
         <v/>
       </c>
@@ -10774,7 +10873,7 @@
       </c>
     </row>
     <row r="71" ht="22.5" customHeight="1">
-      <c r="A71" s="25">
+      <c r="A71" s="78">
         <f>IF($V71="","",INDEX($R$2:$R$401,$V71))</f>
         <v/>
       </c>
@@ -10818,7 +10917,7 @@
       </c>
     </row>
     <row r="72" ht="22.5" customHeight="1">
-      <c r="A72" s="35">
+      <c r="A72" s="85">
         <f>IF($V72="","",INDEX($R$2:$R$401,$V72))</f>
         <v/>
       </c>
@@ -10862,7 +10961,7 @@
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" s="25">
+      <c r="A73" s="78">
         <f>IF($V73="","",INDEX($R$2:$R$401,$V73))</f>
         <v/>
       </c>
@@ -10906,7 +11005,7 @@
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
-      <c r="A74" s="35">
+      <c r="A74" s="85">
         <f>IF($V74="","",INDEX($R$2:$R$401,$V74))</f>
         <v/>
       </c>
@@ -10950,7 +11049,7 @@
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
-      <c r="A75" s="25">
+      <c r="A75" s="78">
         <f>IF($V75="","",INDEX($R$2:$R$401,$V75))</f>
         <v/>
       </c>
@@ -10994,7 +11093,7 @@
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
-      <c r="A76" s="35">
+      <c r="A76" s="85">
         <f>IF($V76="","",INDEX($R$2:$R$401,$V76))</f>
         <v/>
       </c>
@@ -11038,7 +11137,7 @@
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1">
-      <c r="A77" s="25">
+      <c r="A77" s="78">
         <f>IF($V77="","",INDEX($R$2:$R$401,$V77))</f>
         <v/>
       </c>
@@ -11082,7 +11181,7 @@
       </c>
     </row>
     <row r="78" ht="22.5" customHeight="1">
-      <c r="A78" s="35">
+      <c r="A78" s="85">
         <f>IF($V78="","",INDEX($R$2:$R$401,$V78))</f>
         <v/>
       </c>
@@ -11126,7 +11225,7 @@
       </c>
     </row>
     <row r="79" ht="22.5" customHeight="1">
-      <c r="A79" s="25">
+      <c r="A79" s="78">
         <f>IF($V79="","",INDEX($R$2:$R$401,$V79))</f>
         <v/>
       </c>
@@ -11170,7 +11269,7 @@
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
-      <c r="A80" s="35">
+      <c r="A80" s="85">
         <f>IF($V80="","",INDEX($R$2:$R$401,$V80))</f>
         <v/>
       </c>
@@ -11214,7 +11313,7 @@
       </c>
     </row>
     <row r="81" ht="22.5" customHeight="1">
-      <c r="A81" s="25">
+      <c r="A81" s="78">
         <f>IF($V81="","",INDEX($R$2:$R$401,$V81))</f>
         <v/>
       </c>
@@ -11258,7 +11357,7 @@
       </c>
     </row>
     <row r="82" ht="22.5" customHeight="1">
-      <c r="A82" s="35">
+      <c r="A82" s="85">
         <f>IF($V82="","",INDEX($R$2:$R$401,$V82))</f>
         <v/>
       </c>
@@ -11302,7 +11401,7 @@
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1">
-      <c r="A83" s="25">
+      <c r="A83" s="78">
         <f>IF($V83="","",INDEX($R$2:$R$401,$V83))</f>
         <v/>
       </c>
@@ -11346,7 +11445,7 @@
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
-      <c r="A84" s="35">
+      <c r="A84" s="85">
         <f>IF($V84="","",INDEX($R$2:$R$401,$V84))</f>
         <v/>
       </c>
@@ -11390,7 +11489,7 @@
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
-      <c r="A85" s="25">
+      <c r="A85" s="78">
         <f>IF($V85="","",INDEX($R$2:$R$401,$V85))</f>
         <v/>
       </c>
@@ -11434,7 +11533,7 @@
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
-      <c r="A86" s="35">
+      <c r="A86" s="85">
         <f>IF($V86="","",INDEX($R$2:$R$401,$V86))</f>
         <v/>
       </c>
@@ -11478,7 +11577,7 @@
       </c>
     </row>
     <row r="87" ht="22.5" customHeight="1">
-      <c r="A87" s="25">
+      <c r="A87" s="78">
         <f>IF($V87="","",INDEX($R$2:$R$401,$V87))</f>
         <v/>
       </c>
@@ -11522,7 +11621,7 @@
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
-      <c r="A88" s="35">
+      <c r="A88" s="85">
         <f>IF($V88="","",INDEX($R$2:$R$401,$V88))</f>
         <v/>
       </c>
@@ -11566,7 +11665,7 @@
       </c>
     </row>
     <row r="89" ht="22.5" customHeight="1">
-      <c r="A89" s="25">
+      <c r="A89" s="78">
         <f>IF($V89="","",INDEX($R$2:$R$401,$V89))</f>
         <v/>
       </c>
@@ -11610,7 +11709,7 @@
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
-      <c r="A90" s="35">
+      <c r="A90" s="85">
         <f>IF($V90="","",INDEX($R$2:$R$401,$V90))</f>
         <v/>
       </c>
@@ -11654,7 +11753,7 @@
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
-      <c r="A91" s="25">
+      <c r="A91" s="78">
         <f>IF($V91="","",INDEX($R$2:$R$401,$V91))</f>
         <v/>
       </c>
@@ -11698,7 +11797,7 @@
       </c>
     </row>
     <row r="92" ht="22.5" customHeight="1">
-      <c r="A92" s="35">
+      <c r="A92" s="85">
         <f>IF($V92="","",INDEX($R$2:$R$401,$V92))</f>
         <v/>
       </c>
@@ -11742,7 +11841,7 @@
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1">
-      <c r="A93" s="25">
+      <c r="A93" s="78">
         <f>IF($V93="","",INDEX($R$2:$R$401,$V93))</f>
         <v/>
       </c>
@@ -11786,7 +11885,7 @@
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
-      <c r="A94" s="35">
+      <c r="A94" s="85">
         <f>IF($V94="","",INDEX($R$2:$R$401,$V94))</f>
         <v/>
       </c>
@@ -11830,7 +11929,7 @@
       </c>
     </row>
     <row r="95" ht="22.5" customHeight="1">
-      <c r="A95" s="25">
+      <c r="A95" s="78">
         <f>IF($V95="","",INDEX($R$2:$R$401,$V95))</f>
         <v/>
       </c>
@@ -11874,7 +11973,7 @@
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
-      <c r="A96" s="35">
+      <c r="A96" s="85">
         <f>IF($V96="","",INDEX($R$2:$R$401,$V96))</f>
         <v/>
       </c>
@@ -11918,7 +12017,7 @@
       </c>
     </row>
     <row r="97" ht="22.5" customHeight="1">
-      <c r="A97" s="25">
+      <c r="A97" s="78">
         <f>IF($V97="","",INDEX($R$2:$R$401,$V97))</f>
         <v/>
       </c>
@@ -11962,7 +12061,7 @@
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1">
-      <c r="A98" s="35">
+      <c r="A98" s="85">
         <f>IF($V98="","",INDEX($R$2:$R$401,$V98))</f>
         <v/>
       </c>
@@ -12006,7 +12105,7 @@
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
-      <c r="A99" s="25">
+      <c r="A99" s="78">
         <f>IF($V99="","",INDEX($R$2:$R$401,$V99))</f>
         <v/>
       </c>
@@ -12050,7 +12149,7 @@
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
-      <c r="A100" s="35">
+      <c r="A100" s="85">
         <f>IF($V100="","",INDEX($R$2:$R$401,$V100))</f>
         <v/>
       </c>
@@ -12094,7 +12193,7 @@
       </c>
     </row>
     <row r="101" ht="22.5" customHeight="1">
-      <c r="A101" s="25">
+      <c r="A101" s="78">
         <f>IF($V101="","",INDEX($R$2:$R$401,$V101))</f>
         <v/>
       </c>
@@ -12138,7 +12237,7 @@
       </c>
     </row>
     <row r="102" ht="22.5" customHeight="1">
-      <c r="A102" s="35">
+      <c r="A102" s="85">
         <f>IF($V102="","",INDEX($R$2:$R$401,$V102))</f>
         <v/>
       </c>
@@ -12182,7 +12281,7 @@
       </c>
     </row>
     <row r="103" ht="22.5" customHeight="1">
-      <c r="A103" s="25">
+      <c r="A103" s="78">
         <f>IF($V103="","",INDEX($R$2:$R$401,$V103))</f>
         <v/>
       </c>
@@ -12226,7 +12325,7 @@
       </c>
     </row>
     <row r="104" ht="22.5" customHeight="1">
-      <c r="A104" s="35">
+      <c r="A104" s="85">
         <f>IF($V104="","",INDEX($R$2:$R$401,$V104))</f>
         <v/>
       </c>
@@ -12270,7 +12369,7 @@
       </c>
     </row>
     <row r="105" ht="22.5" customHeight="1">
-      <c r="A105" s="25">
+      <c r="A105" s="78">
         <f>IF($V105="","",INDEX($R$2:$R$401,$V105))</f>
         <v/>
       </c>
@@ -12314,7 +12413,7 @@
       </c>
     </row>
     <row r="106" ht="22.5" customHeight="1">
-      <c r="A106" s="35">
+      <c r="A106" s="85">
         <f>IF($V106="","",INDEX($R$2:$R$401,$V106))</f>
         <v/>
       </c>
@@ -12358,7 +12457,7 @@
       </c>
     </row>
     <row r="107" ht="22.5" customHeight="1">
-      <c r="A107" s="25">
+      <c r="A107" s="78">
         <f>IF($V107="","",INDEX($R$2:$R$401,$V107))</f>
         <v/>
       </c>
@@ -12402,7 +12501,7 @@
       </c>
     </row>
     <row r="108" ht="22.5" customHeight="1">
-      <c r="A108" s="35">
+      <c r="A108" s="85">
         <f>IF($V108="","",INDEX($R$2:$R$401,$V108))</f>
         <v/>
       </c>
@@ -12446,7 +12545,7 @@
       </c>
     </row>
     <row r="109" ht="22.5" customHeight="1">
-      <c r="A109" s="25">
+      <c r="A109" s="78">
         <f>IF($V109="","",INDEX($R$2:$R$401,$V109))</f>
         <v/>
       </c>
@@ -12490,7 +12589,7 @@
       </c>
     </row>
     <row r="110" ht="22.5" customHeight="1">
-      <c r="A110" s="35">
+      <c r="A110" s="85">
         <f>IF($V110="","",INDEX($R$2:$R$401,$V110))</f>
         <v/>
       </c>
@@ -12534,7 +12633,7 @@
       </c>
     </row>
     <row r="111" ht="22.5" customHeight="1">
-      <c r="A111" s="25">
+      <c r="A111" s="78">
         <f>IF($V111="","",INDEX($R$2:$R$401,$V111))</f>
         <v/>
       </c>
@@ -12578,7 +12677,7 @@
       </c>
     </row>
     <row r="112" ht="22.5" customHeight="1">
-      <c r="A112" s="35">
+      <c r="A112" s="85">
         <f>IF($V112="","",INDEX($R$2:$R$401,$V112))</f>
         <v/>
       </c>
@@ -12622,7 +12721,7 @@
       </c>
     </row>
     <row r="113" ht="22.5" customHeight="1">
-      <c r="A113" s="25">
+      <c r="A113" s="78">
         <f>IF($V113="","",INDEX($R$2:$R$401,$V113))</f>
         <v/>
       </c>
@@ -12666,7 +12765,7 @@
       </c>
     </row>
     <row r="114" ht="22.5" customHeight="1">
-      <c r="A114" s="35">
+      <c r="A114" s="85">
         <f>IF($V114="","",INDEX($R$2:$R$401,$V114))</f>
         <v/>
       </c>
@@ -12710,7 +12809,7 @@
       </c>
     </row>
     <row r="115" ht="22.5" customHeight="1">
-      <c r="A115" s="25">
+      <c r="A115" s="78">
         <f>IF($V115="","",INDEX($R$2:$R$401,$V115))</f>
         <v/>
       </c>
@@ -12754,7 +12853,7 @@
       </c>
     </row>
     <row r="116" ht="22.5" customHeight="1">
-      <c r="A116" s="35">
+      <c r="A116" s="85">
         <f>IF($V116="","",INDEX($R$2:$R$401,$V116))</f>
         <v/>
       </c>
@@ -12798,7 +12897,7 @@
       </c>
     </row>
     <row r="117" ht="22.5" customHeight="1">
-      <c r="A117" s="25">
+      <c r="A117" s="78">
         <f>IF($V117="","",INDEX($R$2:$R$401,$V117))</f>
         <v/>
       </c>
@@ -12842,7 +12941,7 @@
       </c>
     </row>
     <row r="118" ht="22.5" customHeight="1">
-      <c r="A118" s="35">
+      <c r="A118" s="85">
         <f>IF($V118="","",INDEX($R$2:$R$401,$V118))</f>
         <v/>
       </c>
@@ -12886,7 +12985,7 @@
       </c>
     </row>
     <row r="119" ht="22.5" customHeight="1">
-      <c r="A119" s="25">
+      <c r="A119" s="78">
         <f>IF($V119="","",INDEX($R$2:$R$401,$V119))</f>
         <v/>
       </c>
@@ -12930,7 +13029,7 @@
       </c>
     </row>
     <row r="120" ht="22.5" customHeight="1">
-      <c r="A120" s="35">
+      <c r="A120" s="85">
         <f>IF($V120="","",INDEX($R$2:$R$401,$V120))</f>
         <v/>
       </c>
@@ -12974,7 +13073,7 @@
       </c>
     </row>
     <row r="121" ht="22.5" customHeight="1">
-      <c r="A121" s="25">
+      <c r="A121" s="78">
         <f>IF($V121="","",INDEX($R$2:$R$401,$V121))</f>
         <v/>
       </c>
@@ -13018,7 +13117,7 @@
       </c>
     </row>
     <row r="122" ht="22.5" customHeight="1">
-      <c r="A122" s="35">
+      <c r="A122" s="85">
         <f>IF($V122="","",INDEX($R$2:$R$401,$V122))</f>
         <v/>
       </c>
@@ -13062,7 +13161,7 @@
       </c>
     </row>
     <row r="123" ht="22.5" customHeight="1">
-      <c r="A123" s="25">
+      <c r="A123" s="78">
         <f>IF($V123="","",INDEX($R$2:$R$401,$V123))</f>
         <v/>
       </c>
@@ -13106,7 +13205,7 @@
       </c>
     </row>
     <row r="124" ht="22.5" customHeight="1">
-      <c r="A124" s="35">
+      <c r="A124" s="85">
         <f>IF($V124="","",INDEX($R$2:$R$401,$V124))</f>
         <v/>
       </c>
@@ -13150,7 +13249,7 @@
       </c>
     </row>
     <row r="125" ht="22.5" customHeight="1">
-      <c r="A125" s="25">
+      <c r="A125" s="78">
         <f>IF($V125="","",INDEX($R$2:$R$401,$V125))</f>
         <v/>
       </c>
@@ -13194,7 +13293,7 @@
       </c>
     </row>
     <row r="126" ht="22.5" customHeight="1">
-      <c r="A126" s="35">
+      <c r="A126" s="85">
         <f>IF($V126="","",INDEX($R$2:$R$401,$V126))</f>
         <v/>
       </c>
@@ -13238,7 +13337,7 @@
       </c>
     </row>
     <row r="127" ht="22.5" customHeight="1">
-      <c r="A127" s="25">
+      <c r="A127" s="78">
         <f>IF($V127="","",INDEX($R$2:$R$401,$V127))</f>
         <v/>
       </c>
@@ -13282,7 +13381,7 @@
       </c>
     </row>
     <row r="128" ht="22.5" customHeight="1">
-      <c r="A128" s="35">
+      <c r="A128" s="85">
         <f>IF($V128="","",INDEX($R$2:$R$401,$V128))</f>
         <v/>
       </c>
@@ -13326,7 +13425,7 @@
       </c>
     </row>
     <row r="129" ht="22.5" customHeight="1">
-      <c r="A129" s="25">
+      <c r="A129" s="78">
         <f>IF($V129="","",INDEX($R$2:$R$401,$V129))</f>
         <v/>
       </c>
@@ -13370,7 +13469,7 @@
       </c>
     </row>
     <row r="130" ht="22.5" customHeight="1">
-      <c r="A130" s="35">
+      <c r="A130" s="85">
         <f>IF($V130="","",INDEX($R$2:$R$401,$V130))</f>
         <v/>
       </c>
@@ -13414,7 +13513,7 @@
       </c>
     </row>
     <row r="131" ht="22.5" customHeight="1">
-      <c r="A131" s="25">
+      <c r="A131" s="78">
         <f>IF($V131="","",INDEX($R$2:$R$401,$V131))</f>
         <v/>
       </c>
@@ -13458,7 +13557,7 @@
       </c>
     </row>
     <row r="132" ht="22.5" customHeight="1">
-      <c r="A132" s="35">
+      <c r="A132" s="85">
         <f>IF($V132="","",INDEX($R$2:$R$401,$V132))</f>
         <v/>
       </c>
@@ -13502,7 +13601,7 @@
       </c>
     </row>
     <row r="133" ht="22.5" customHeight="1">
-      <c r="A133" s="25">
+      <c r="A133" s="78">
         <f>IF($V133="","",INDEX($R$2:$R$401,$V133))</f>
         <v/>
       </c>
@@ -13546,7 +13645,7 @@
       </c>
     </row>
     <row r="134" ht="22.5" customHeight="1">
-      <c r="A134" s="35">
+      <c r="A134" s="85">
         <f>IF($V134="","",INDEX($R$2:$R$401,$V134))</f>
         <v/>
       </c>
@@ -13590,7 +13689,7 @@
       </c>
     </row>
     <row r="135" ht="22.5" customHeight="1">
-      <c r="A135" s="25">
+      <c r="A135" s="78">
         <f>IF($V135="","",INDEX($R$2:$R$401,$V135))</f>
         <v/>
       </c>
@@ -13634,7 +13733,7 @@
       </c>
     </row>
     <row r="136" ht="22.5" customHeight="1">
-      <c r="A136" s="35">
+      <c r="A136" s="85">
         <f>IF($V136="","",INDEX($R$2:$R$401,$V136))</f>
         <v/>
       </c>
@@ -13678,7 +13777,7 @@
       </c>
     </row>
     <row r="137" ht="22.5" customHeight="1">
-      <c r="A137" s="25">
+      <c r="A137" s="78">
         <f>IF($V137="","",INDEX($R$2:$R$401,$V137))</f>
         <v/>
       </c>
@@ -13722,7 +13821,7 @@
       </c>
     </row>
     <row r="138" ht="22.5" customHeight="1">
-      <c r="A138" s="35">
+      <c r="A138" s="85">
         <f>IF($V138="","",INDEX($R$2:$R$401,$V138))</f>
         <v/>
       </c>
@@ -13766,7 +13865,7 @@
       </c>
     </row>
     <row r="139" ht="22.5" customHeight="1">
-      <c r="A139" s="25">
+      <c r="A139" s="78">
         <f>IF($V139="","",INDEX($R$2:$R$401,$V139))</f>
         <v/>
       </c>
@@ -13810,7 +13909,7 @@
       </c>
     </row>
     <row r="140" ht="22.5" customHeight="1">
-      <c r="A140" s="35">
+      <c r="A140" s="85">
         <f>IF($V140="","",INDEX($R$2:$R$401,$V140))</f>
         <v/>
       </c>
@@ -13854,7 +13953,7 @@
       </c>
     </row>
     <row r="141" ht="22.5" customHeight="1">
-      <c r="A141" s="25">
+      <c r="A141" s="78">
         <f>IF($V141="","",INDEX($R$2:$R$401,$V141))</f>
         <v/>
       </c>
@@ -13898,7 +13997,7 @@
       </c>
     </row>
     <row r="142" ht="22.5" customHeight="1">
-      <c r="A142" s="35">
+      <c r="A142" s="85">
         <f>IF($V142="","",INDEX($R$2:$R$401,$V142))</f>
         <v/>
       </c>
@@ -13942,7 +14041,7 @@
       </c>
     </row>
     <row r="143" ht="22.5" customHeight="1">
-      <c r="A143" s="25">
+      <c r="A143" s="78">
         <f>IF($V143="","",INDEX($R$2:$R$401,$V143))</f>
         <v/>
       </c>
@@ -13986,7 +14085,7 @@
       </c>
     </row>
     <row r="144" ht="22.5" customHeight="1">
-      <c r="A144" s="35">
+      <c r="A144" s="85">
         <f>IF($V144="","",INDEX($R$2:$R$401,$V144))</f>
         <v/>
       </c>
@@ -14030,7 +14129,7 @@
       </c>
     </row>
     <row r="145" ht="22.5" customHeight="1">
-      <c r="A145" s="25">
+      <c r="A145" s="78">
         <f>IF($V145="","",INDEX($R$2:$R$401,$V145))</f>
         <v/>
       </c>
@@ -14074,7 +14173,7 @@
       </c>
     </row>
     <row r="146" ht="22.5" customHeight="1">
-      <c r="A146" s="35">
+      <c r="A146" s="85">
         <f>IF($V146="","",INDEX($R$2:$R$401,$V146))</f>
         <v/>
       </c>
@@ -14118,7 +14217,7 @@
       </c>
     </row>
     <row r="147" ht="22.5" customHeight="1">
-      <c r="A147" s="25">
+      <c r="A147" s="78">
         <f>IF($V147="","",INDEX($R$2:$R$401,$V147))</f>
         <v/>
       </c>
@@ -14162,7 +14261,7 @@
       </c>
     </row>
     <row r="148" ht="22.5" customHeight="1">
-      <c r="A148" s="35">
+      <c r="A148" s="85">
         <f>IF($V148="","",INDEX($R$2:$R$401,$V148))</f>
         <v/>
       </c>
@@ -14206,7 +14305,7 @@
       </c>
     </row>
     <row r="149" ht="22.5" customHeight="1">
-      <c r="A149" s="25">
+      <c r="A149" s="78">
         <f>IF($V149="","",INDEX($R$2:$R$401,$V149))</f>
         <v/>
       </c>
@@ -14250,7 +14349,7 @@
       </c>
     </row>
     <row r="150" ht="22.5" customHeight="1">
-      <c r="A150" s="35">
+      <c r="A150" s="85">
         <f>IF($V150="","",INDEX($R$2:$R$401,$V150))</f>
         <v/>
       </c>
@@ -14294,7 +14393,7 @@
       </c>
     </row>
     <row r="151" ht="22.5" customHeight="1">
-      <c r="A151" s="25">
+      <c r="A151" s="78">
         <f>IF($V151="","",INDEX($R$2:$R$401,$V151))</f>
         <v/>
       </c>
@@ -14338,7 +14437,7 @@
       </c>
     </row>
     <row r="152" ht="22.5" customHeight="1">
-      <c r="A152" s="35">
+      <c r="A152" s="85">
         <f>IF($V152="","",INDEX($R$2:$R$401,$V152))</f>
         <v/>
       </c>
@@ -14382,7 +14481,7 @@
       </c>
     </row>
     <row r="153" ht="22.5" customHeight="1">
-      <c r="A153" s="25">
+      <c r="A153" s="78">
         <f>IF($V153="","",INDEX($R$2:$R$401,$V153))</f>
         <v/>
       </c>
@@ -14426,7 +14525,7 @@
       </c>
     </row>
     <row r="154" ht="22.5" customHeight="1">
-      <c r="A154" s="35">
+      <c r="A154" s="85">
         <f>IF($V154="","",INDEX($R$2:$R$401,$V154))</f>
         <v/>
       </c>
@@ -14470,7 +14569,7 @@
       </c>
     </row>
     <row r="155" ht="22.5" customHeight="1">
-      <c r="A155" s="25">
+      <c r="A155" s="78">
         <f>IF($V155="","",INDEX($R$2:$R$401,$V155))</f>
         <v/>
       </c>
@@ -14514,7 +14613,7 @@
       </c>
     </row>
     <row r="156" ht="22.5" customHeight="1">
-      <c r="A156" s="35">
+      <c r="A156" s="85">
         <f>IF($V156="","",INDEX($R$2:$R$401,$V156))</f>
         <v/>
       </c>
@@ -14558,7 +14657,7 @@
       </c>
     </row>
     <row r="157" ht="22.5" customHeight="1">
-      <c r="A157" s="25">
+      <c r="A157" s="78">
         <f>IF($V157="","",INDEX($R$2:$R$401,$V157))</f>
         <v/>
       </c>
@@ -14602,7 +14701,7 @@
       </c>
     </row>
     <row r="158" ht="22.5" customHeight="1">
-      <c r="A158" s="35">
+      <c r="A158" s="85">
         <f>IF($V158="","",INDEX($R$2:$R$401,$V158))</f>
         <v/>
       </c>
@@ -14646,7 +14745,7 @@
       </c>
     </row>
     <row r="159" ht="22.5" customHeight="1">
-      <c r="A159" s="25">
+      <c r="A159" s="78">
         <f>IF($V159="","",INDEX($R$2:$R$401,$V159))</f>
         <v/>
       </c>
@@ -14690,7 +14789,7 @@
       </c>
     </row>
     <row r="160" ht="22.5" customHeight="1">
-      <c r="A160" s="35">
+      <c r="A160" s="85">
         <f>IF($V160="","",INDEX($R$2:$R$401,$V160))</f>
         <v/>
       </c>
@@ -14734,7 +14833,7 @@
       </c>
     </row>
     <row r="161" ht="22.5" customHeight="1">
-      <c r="A161" s="25">
+      <c r="A161" s="78">
         <f>IF($V161="","",INDEX($R$2:$R$401,$V161))</f>
         <v/>
       </c>
@@ -14778,7 +14877,7 @@
       </c>
     </row>
     <row r="162" ht="22.5" customHeight="1">
-      <c r="A162" s="35">
+      <c r="A162" s="85">
         <f>IF($V162="","",INDEX($R$2:$R$401,$V162))</f>
         <v/>
       </c>
@@ -14822,7 +14921,7 @@
       </c>
     </row>
     <row r="163" ht="22.5" customHeight="1">
-      <c r="A163" s="25">
+      <c r="A163" s="78">
         <f>IF($V163="","",INDEX($R$2:$R$401,$V163))</f>
         <v/>
       </c>
@@ -14866,7 +14965,7 @@
       </c>
     </row>
     <row r="164" ht="22.5" customHeight="1">
-      <c r="A164" s="35">
+      <c r="A164" s="85">
         <f>IF($V164="","",INDEX($R$2:$R$401,$V164))</f>
         <v/>
       </c>
@@ -14910,7 +15009,7 @@
       </c>
     </row>
     <row r="165" ht="22.5" customHeight="1">
-      <c r="A165" s="25">
+      <c r="A165" s="78">
         <f>IF($V165="","",INDEX($R$2:$R$401,$V165))</f>
         <v/>
       </c>
@@ -14954,7 +15053,7 @@
       </c>
     </row>
     <row r="166" ht="22.5" customHeight="1">
-      <c r="A166" s="35">
+      <c r="A166" s="85">
         <f>IF($V166="","",INDEX($R$2:$R$401,$V166))</f>
         <v/>
       </c>
@@ -14998,7 +15097,7 @@
       </c>
     </row>
     <row r="167" ht="22.5" customHeight="1">
-      <c r="A167" s="25">
+      <c r="A167" s="78">
         <f>IF($V167="","",INDEX($R$2:$R$401,$V167))</f>
         <v/>
       </c>
@@ -15042,7 +15141,7 @@
       </c>
     </row>
     <row r="168" ht="22.5" customHeight="1">
-      <c r="A168" s="35">
+      <c r="A168" s="85">
         <f>IF($V168="","",INDEX($R$2:$R$401,$V168))</f>
         <v/>
       </c>
@@ -15086,7 +15185,7 @@
       </c>
     </row>
     <row r="169" ht="22.5" customHeight="1">
-      <c r="A169" s="25">
+      <c r="A169" s="78">
         <f>IF($V169="","",INDEX($R$2:$R$401,$V169))</f>
         <v/>
       </c>
@@ -15130,7 +15229,7 @@
       </c>
     </row>
     <row r="170" ht="22.5" customHeight="1">
-      <c r="A170" s="35">
+      <c r="A170" s="85">
         <f>IF($V170="","",INDEX($R$2:$R$401,$V170))</f>
         <v/>
       </c>
@@ -15174,7 +15273,7 @@
       </c>
     </row>
     <row r="171" ht="22.5" customHeight="1">
-      <c r="A171" s="25">
+      <c r="A171" s="78">
         <f>IF($V171="","",INDEX($R$2:$R$401,$V171))</f>
         <v/>
       </c>
@@ -15218,7 +15317,7 @@
       </c>
     </row>
     <row r="172" ht="22.5" customHeight="1">
-      <c r="A172" s="35">
+      <c r="A172" s="85">
         <f>IF($V172="","",INDEX($R$2:$R$401,$V172))</f>
         <v/>
       </c>
@@ -15262,7 +15361,7 @@
       </c>
     </row>
     <row r="173" ht="22.5" customHeight="1">
-      <c r="A173" s="25">
+      <c r="A173" s="78">
         <f>IF($V173="","",INDEX($R$2:$R$401,$V173))</f>
         <v/>
       </c>
@@ -15306,7 +15405,7 @@
       </c>
     </row>
     <row r="174" ht="22.5" customHeight="1">
-      <c r="A174" s="35">
+      <c r="A174" s="85">
         <f>IF($V174="","",INDEX($R$2:$R$401,$V174))</f>
         <v/>
       </c>
@@ -15350,7 +15449,7 @@
       </c>
     </row>
     <row r="175" ht="22.5" customHeight="1">
-      <c r="A175" s="25">
+      <c r="A175" s="78">
         <f>IF($V175="","",INDEX($R$2:$R$401,$V175))</f>
         <v/>
       </c>
@@ -15394,7 +15493,7 @@
       </c>
     </row>
     <row r="176" ht="22.5" customHeight="1">
-      <c r="A176" s="35">
+      <c r="A176" s="85">
         <f>IF($V176="","",INDEX($R$2:$R$401,$V176))</f>
         <v/>
       </c>
@@ -15438,7 +15537,7 @@
       </c>
     </row>
     <row r="177" ht="22.5" customHeight="1">
-      <c r="A177" s="25">
+      <c r="A177" s="78">
         <f>IF($V177="","",INDEX($R$2:$R$401,$V177))</f>
         <v/>
       </c>
@@ -15482,7 +15581,7 @@
       </c>
     </row>
     <row r="178" ht="22.5" customHeight="1">
-      <c r="A178" s="35">
+      <c r="A178" s="85">
         <f>IF($V178="","",INDEX($R$2:$R$401,$V178))</f>
         <v/>
       </c>
@@ -15526,7 +15625,7 @@
       </c>
     </row>
     <row r="179" ht="22.5" customHeight="1">
-      <c r="A179" s="25">
+      <c r="A179" s="78">
         <f>IF($V179="","",INDEX($R$2:$R$401,$V179))</f>
         <v/>
       </c>
@@ -15570,7 +15669,7 @@
       </c>
     </row>
     <row r="180" ht="22.5" customHeight="1">
-      <c r="A180" s="35">
+      <c r="A180" s="85">
         <f>IF($V180="","",INDEX($R$2:$R$401,$V180))</f>
         <v/>
       </c>
@@ -15614,7 +15713,7 @@
       </c>
     </row>
     <row r="181" ht="22.5" customHeight="1">
-      <c r="A181" s="25">
+      <c r="A181" s="78">
         <f>IF($V181="","",INDEX($R$2:$R$401,$V181))</f>
         <v/>
       </c>
@@ -15658,7 +15757,7 @@
       </c>
     </row>
     <row r="182" ht="22.5" customHeight="1">
-      <c r="A182" s="35">
+      <c r="A182" s="85">
         <f>IF($V182="","",INDEX($R$2:$R$401,$V182))</f>
         <v/>
       </c>
@@ -15702,7 +15801,7 @@
       </c>
     </row>
     <row r="183" ht="22.5" customHeight="1">
-      <c r="A183" s="25">
+      <c r="A183" s="78">
         <f>IF($V183="","",INDEX($R$2:$R$401,$V183))</f>
         <v/>
       </c>
@@ -15746,7 +15845,7 @@
       </c>
     </row>
     <row r="184" ht="22.5" customHeight="1">
-      <c r="A184" s="35">
+      <c r="A184" s="85">
         <f>IF($V184="","",INDEX($R$2:$R$401,$V184))</f>
         <v/>
       </c>
@@ -15790,7 +15889,7 @@
       </c>
     </row>
     <row r="185" ht="22.5" customHeight="1">
-      <c r="A185" s="25">
+      <c r="A185" s="78">
         <f>IF($V185="","",INDEX($R$2:$R$401,$V185))</f>
         <v/>
       </c>
@@ -15834,7 +15933,7 @@
       </c>
     </row>
     <row r="186" ht="22.5" customHeight="1">
-      <c r="A186" s="35">
+      <c r="A186" s="85">
         <f>IF($V186="","",INDEX($R$2:$R$401,$V186))</f>
         <v/>
       </c>
@@ -15878,7 +15977,7 @@
       </c>
     </row>
     <row r="187" ht="22.5" customHeight="1">
-      <c r="A187" s="25">
+      <c r="A187" s="78">
         <f>IF($V187="","",INDEX($R$2:$R$401,$V187))</f>
         <v/>
       </c>
@@ -15922,7 +16021,7 @@
       </c>
     </row>
     <row r="188" ht="22.5" customHeight="1">
-      <c r="A188" s="35">
+      <c r="A188" s="85">
         <f>IF($V188="","",INDEX($R$2:$R$401,$V188))</f>
         <v/>
       </c>
@@ -15966,7 +16065,7 @@
       </c>
     </row>
     <row r="189" ht="22.5" customHeight="1">
-      <c r="A189" s="25">
+      <c r="A189" s="78">
         <f>IF($V189="","",INDEX($R$2:$R$401,$V189))</f>
         <v/>
       </c>
@@ -16010,7 +16109,7 @@
       </c>
     </row>
     <row r="190" ht="22.5" customHeight="1">
-      <c r="A190" s="35">
+      <c r="A190" s="85">
         <f>IF($V190="","",INDEX($R$2:$R$401,$V190))</f>
         <v/>
       </c>
@@ -16054,7 +16153,7 @@
       </c>
     </row>
     <row r="191" ht="22.5" customHeight="1">
-      <c r="A191" s="25">
+      <c r="A191" s="78">
         <f>IF($V191="","",INDEX($R$2:$R$401,$V191))</f>
         <v/>
       </c>
@@ -16098,7 +16197,7 @@
       </c>
     </row>
     <row r="192" ht="22.5" customHeight="1">
-      <c r="A192" s="35">
+      <c r="A192" s="85">
         <f>IF($V192="","",INDEX($R$2:$R$401,$V192))</f>
         <v/>
       </c>
@@ -16142,7 +16241,7 @@
       </c>
     </row>
     <row r="193" ht="22.5" customHeight="1">
-      <c r="A193" s="25">
+      <c r="A193" s="78">
         <f>IF($V193="","",INDEX($R$2:$R$401,$V193))</f>
         <v/>
       </c>
@@ -16186,7 +16285,7 @@
       </c>
     </row>
     <row r="194" ht="22.5" customHeight="1">
-      <c r="A194" s="35">
+      <c r="A194" s="85">
         <f>IF($V194="","",INDEX($R$2:$R$401,$V194))</f>
         <v/>
       </c>
@@ -16230,7 +16329,7 @@
       </c>
     </row>
     <row r="195" ht="22.5" customHeight="1">
-      <c r="A195" s="25">
+      <c r="A195" s="78">
         <f>IF($V195="","",INDEX($R$2:$R$401,$V195))</f>
         <v/>
       </c>
@@ -16274,7 +16373,7 @@
       </c>
     </row>
     <row r="196" ht="22.5" customHeight="1">
-      <c r="A196" s="35">
+      <c r="A196" s="85">
         <f>IF($V196="","",INDEX($R$2:$R$401,$V196))</f>
         <v/>
       </c>
@@ -16318,7 +16417,7 @@
       </c>
     </row>
     <row r="197" ht="22.5" customHeight="1">
-      <c r="A197" s="25">
+      <c r="A197" s="78">
         <f>IF($V197="","",INDEX($R$2:$R$401,$V197))</f>
         <v/>
       </c>
@@ -16362,7 +16461,7 @@
       </c>
     </row>
     <row r="198" ht="22.5" customHeight="1">
-      <c r="A198" s="35">
+      <c r="A198" s="85">
         <f>IF($V198="","",INDEX($R$2:$R$401,$V198))</f>
         <v/>
       </c>
@@ -16406,7 +16505,7 @@
       </c>
     </row>
     <row r="199" ht="22.5" customHeight="1">
-      <c r="A199" s="25">
+      <c r="A199" s="78">
         <f>IF($V199="","",INDEX($R$2:$R$401,$V199))</f>
         <v/>
       </c>
@@ -16450,7 +16549,7 @@
       </c>
     </row>
     <row r="200" ht="22.5" customHeight="1">
-      <c r="A200" s="35">
+      <c r="A200" s="85">
         <f>IF($V200="","",INDEX($R$2:$R$401,$V200))</f>
         <v/>
       </c>
@@ -16494,7 +16593,7 @@
       </c>
     </row>
     <row r="201" ht="22.5" customHeight="1">
-      <c r="A201" s="25">
+      <c r="A201" s="78">
         <f>IF($V201="","",INDEX($R$2:$R$401,$V201))</f>
         <v/>
       </c>
@@ -16538,7 +16637,7 @@
       </c>
     </row>
     <row r="202" ht="22.5" customHeight="1">
-      <c r="A202" s="35">
+      <c r="A202" s="85">
         <f>IF($V202="","",INDEX($R$2:$R$401,$V202))</f>
         <v/>
       </c>
@@ -16582,7 +16681,7 @@
       </c>
     </row>
     <row r="203" ht="22.5" customHeight="1">
-      <c r="A203" s="25">
+      <c r="A203" s="78">
         <f>IF($V203="","",INDEX($R$2:$R$401,$V203))</f>
         <v/>
       </c>
@@ -16626,7 +16725,7 @@
       </c>
     </row>
     <row r="204" ht="22.5" customHeight="1">
-      <c r="A204" s="35">
+      <c r="A204" s="85">
         <f>IF($V204="","",INDEX($R$2:$R$401,$V204))</f>
         <v/>
       </c>
@@ -16670,7 +16769,7 @@
       </c>
     </row>
     <row r="205" ht="22.5" customHeight="1">
-      <c r="A205" s="25">
+      <c r="A205" s="78">
         <f>IF($V205="","",INDEX($R$2:$R$401,$V205))</f>
         <v/>
       </c>
@@ -16714,7 +16813,7 @@
       </c>
     </row>
     <row r="206" ht="22.5" customHeight="1">
-      <c r="A206" s="35">
+      <c r="A206" s="85">
         <f>IF($V206="","",INDEX($R$2:$R$401,$V206))</f>
         <v/>
       </c>
@@ -16758,7 +16857,7 @@
       </c>
     </row>
     <row r="207" ht="22.5" customHeight="1">
-      <c r="A207" s="25">
+      <c r="A207" s="78">
         <f>IF($V207="","",INDEX($R$2:$R$401,$V207))</f>
         <v/>
       </c>
@@ -16802,7 +16901,7 @@
       </c>
     </row>
     <row r="208" ht="22.5" customHeight="1">
-      <c r="A208" s="35">
+      <c r="A208" s="85">
         <f>IF($V208="","",INDEX($R$2:$R$401,$V208))</f>
         <v/>
       </c>
@@ -16846,7 +16945,7 @@
       </c>
     </row>
     <row r="209" ht="22.5" customHeight="1">
-      <c r="A209" s="25">
+      <c r="A209" s="78">
         <f>IF($V209="","",INDEX($R$2:$R$401,$V209))</f>
         <v/>
       </c>
@@ -16890,7 +16989,7 @@
       </c>
     </row>
     <row r="210" ht="22.5" customHeight="1">
-      <c r="A210" s="35">
+      <c r="A210" s="85">
         <f>IF($V210="","",INDEX($R$2:$R$401,$V210))</f>
         <v/>
       </c>
@@ -16934,7 +17033,7 @@
       </c>
     </row>
     <row r="211" ht="22.5" customHeight="1">
-      <c r="A211" s="25">
+      <c r="A211" s="78">
         <f>IF($V211="","",INDEX($R$2:$R$401,$V211))</f>
         <v/>
       </c>
@@ -16978,7 +17077,7 @@
       </c>
     </row>
     <row r="212" ht="22.5" customHeight="1">
-      <c r="A212" s="35">
+      <c r="A212" s="85">
         <f>IF($V212="","",INDEX($R$2:$R$401,$V212))</f>
         <v/>
       </c>
@@ -17022,7 +17121,7 @@
       </c>
     </row>
     <row r="213" ht="22.5" customHeight="1">
-      <c r="A213" s="25">
+      <c r="A213" s="78">
         <f>IF($V213="","",INDEX($R$2:$R$401,$V213))</f>
         <v/>
       </c>
@@ -17066,7 +17165,7 @@
       </c>
     </row>
     <row r="214" ht="22.5" customHeight="1">
-      <c r="A214" s="35">
+      <c r="A214" s="85">
         <f>IF($V214="","",INDEX($R$2:$R$401,$V214))</f>
         <v/>
       </c>
@@ -17110,7 +17209,7 @@
       </c>
     </row>
     <row r="215" ht="22.5" customHeight="1">
-      <c r="A215" s="25">
+      <c r="A215" s="78">
         <f>IF($V215="","",INDEX($R$2:$R$401,$V215))</f>
         <v/>
       </c>
@@ -17154,7 +17253,7 @@
       </c>
     </row>
     <row r="216" ht="22.5" customHeight="1">
-      <c r="A216" s="35">
+      <c r="A216" s="85">
         <f>IF($V216="","",INDEX($R$2:$R$401,$V216))</f>
         <v/>
       </c>
@@ -17198,7 +17297,7 @@
       </c>
     </row>
     <row r="217" ht="22.5" customHeight="1">
-      <c r="A217" s="25">
+      <c r="A217" s="78">
         <f>IF($V217="","",INDEX($R$2:$R$401,$V217))</f>
         <v/>
       </c>
@@ -17242,7 +17341,7 @@
       </c>
     </row>
     <row r="218" ht="22.5" customHeight="1">
-      <c r="A218" s="35">
+      <c r="A218" s="85">
         <f>IF($V218="","",INDEX($R$2:$R$401,$V218))</f>
         <v/>
       </c>
@@ -17286,7 +17385,7 @@
       </c>
     </row>
     <row r="219" ht="22.5" customHeight="1">
-      <c r="A219" s="25">
+      <c r="A219" s="78">
         <f>IF($V219="","",INDEX($R$2:$R$401,$V219))</f>
         <v/>
       </c>
@@ -17330,7 +17429,7 @@
       </c>
     </row>
     <row r="220" ht="22.5" customHeight="1">
-      <c r="A220" s="35">
+      <c r="A220" s="85">
         <f>IF($V220="","",INDEX($R$2:$R$401,$V220))</f>
         <v/>
       </c>
@@ -17374,7 +17473,7 @@
       </c>
     </row>
     <row r="221" ht="22.5" customHeight="1">
-      <c r="A221" s="25">
+      <c r="A221" s="78">
         <f>IF($V221="","",INDEX($R$2:$R$401,$V221))</f>
         <v/>
       </c>
@@ -17418,7 +17517,7 @@
       </c>
     </row>
     <row r="222" ht="22.5" customHeight="1">
-      <c r="A222" s="35">
+      <c r="A222" s="85">
         <f>IF($V222="","",INDEX($R$2:$R$401,$V222))</f>
         <v/>
       </c>
@@ -17462,7 +17561,7 @@
       </c>
     </row>
     <row r="223" ht="22.5" customHeight="1">
-      <c r="A223" s="25">
+      <c r="A223" s="78">
         <f>IF($V223="","",INDEX($R$2:$R$401,$V223))</f>
         <v/>
       </c>
@@ -17506,7 +17605,7 @@
       </c>
     </row>
     <row r="224" ht="22.5" customHeight="1">
-      <c r="A224" s="35">
+      <c r="A224" s="85">
         <f>IF($V224="","",INDEX($R$2:$R$401,$V224))</f>
         <v/>
       </c>
@@ -17550,7 +17649,7 @@
       </c>
     </row>
     <row r="225" ht="22.5" customHeight="1">
-      <c r="A225" s="25">
+      <c r="A225" s="78">
         <f>IF($V225="","",INDEX($R$2:$R$401,$V225))</f>
         <v/>
       </c>
@@ -17594,7 +17693,7 @@
       </c>
     </row>
     <row r="226" ht="22.5" customHeight="1">
-      <c r="A226" s="35">
+      <c r="A226" s="85">
         <f>IF($V226="","",INDEX($R$2:$R$401,$V226))</f>
         <v/>
       </c>
@@ -17638,7 +17737,7 @@
       </c>
     </row>
     <row r="227" ht="22.5" customHeight="1">
-      <c r="A227" s="25">
+      <c r="A227" s="78">
         <f>IF($V227="","",INDEX($R$2:$R$401,$V227))</f>
         <v/>
       </c>
@@ -17682,7 +17781,7 @@
       </c>
     </row>
     <row r="228" ht="22.5" customHeight="1">
-      <c r="A228" s="35">
+      <c r="A228" s="85">
         <f>IF($V228="","",INDEX($R$2:$R$401,$V228))</f>
         <v/>
       </c>
@@ -17726,7 +17825,7 @@
       </c>
     </row>
     <row r="229" ht="22.5" customHeight="1">
-      <c r="A229" s="25">
+      <c r="A229" s="78">
         <f>IF($V229="","",INDEX($R$2:$R$401,$V229))</f>
         <v/>
       </c>
@@ -17770,7 +17869,7 @@
       </c>
     </row>
     <row r="230" ht="22.5" customHeight="1">
-      <c r="A230" s="35">
+      <c r="A230" s="85">
         <f>IF($V230="","",INDEX($R$2:$R$401,$V230))</f>
         <v/>
       </c>
@@ -17814,7 +17913,7 @@
       </c>
     </row>
     <row r="231" ht="22.5" customHeight="1">
-      <c r="A231" s="25">
+      <c r="A231" s="78">
         <f>IF($V231="","",INDEX($R$2:$R$401,$V231))</f>
         <v/>
       </c>
@@ -17858,7 +17957,7 @@
       </c>
     </row>
     <row r="232" ht="22.5" customHeight="1">
-      <c r="A232" s="35">
+      <c r="A232" s="85">
         <f>IF($V232="","",INDEX($R$2:$R$401,$V232))</f>
         <v/>
       </c>
@@ -17902,7 +18001,7 @@
       </c>
     </row>
     <row r="233" ht="22.5" customHeight="1">
-      <c r="A233" s="25">
+      <c r="A233" s="78">
         <f>IF($V233="","",INDEX($R$2:$R$401,$V233))</f>
         <v/>
       </c>
@@ -17946,7 +18045,7 @@
       </c>
     </row>
     <row r="234" ht="22.5" customHeight="1">
-      <c r="A234" s="35">
+      <c r="A234" s="85">
         <f>IF($V234="","",INDEX($R$2:$R$401,$V234))</f>
         <v/>
       </c>
@@ -17990,7 +18089,7 @@
       </c>
     </row>
     <row r="235" ht="22.5" customHeight="1">
-      <c r="A235" s="25">
+      <c r="A235" s="78">
         <f>IF($V235="","",INDEX($R$2:$R$401,$V235))</f>
         <v/>
       </c>
@@ -18034,7 +18133,7 @@
       </c>
     </row>
     <row r="236" ht="22.5" customHeight="1">
-      <c r="A236" s="35">
+      <c r="A236" s="85">
         <f>IF($V236="","",INDEX($R$2:$R$401,$V236))</f>
         <v/>
       </c>
@@ -18078,7 +18177,7 @@
       </c>
     </row>
     <row r="237" ht="22.5" customHeight="1">
-      <c r="A237" s="25">
+      <c r="A237" s="78">
         <f>IF($V237="","",INDEX($R$2:$R$401,$V237))</f>
         <v/>
       </c>
@@ -18122,7 +18221,7 @@
       </c>
     </row>
     <row r="238" ht="22.5" customHeight="1">
-      <c r="A238" s="35">
+      <c r="A238" s="85">
         <f>IF($V238="","",INDEX($R$2:$R$401,$V238))</f>
         <v/>
       </c>
@@ -18166,7 +18265,7 @@
       </c>
     </row>
     <row r="239" ht="22.5" customHeight="1">
-      <c r="A239" s="25">
+      <c r="A239" s="78">
         <f>IF($V239="","",INDEX($R$2:$R$401,$V239))</f>
         <v/>
       </c>
@@ -18210,7 +18309,7 @@
       </c>
     </row>
     <row r="240" ht="22.5" customHeight="1">
-      <c r="A240" s="35">
+      <c r="A240" s="85">
         <f>IF($V240="","",INDEX($R$2:$R$401,$V240))</f>
         <v/>
       </c>
@@ -18254,7 +18353,7 @@
       </c>
     </row>
     <row r="241" ht="22.5" customHeight="1">
-      <c r="A241" s="25">
+      <c r="A241" s="78">
         <f>IF($V241="","",INDEX($R$2:$R$401,$V241))</f>
         <v/>
       </c>
@@ -18298,7 +18397,7 @@
       </c>
     </row>
     <row r="242" ht="22.5" customHeight="1">
-      <c r="A242" s="35">
+      <c r="A242" s="85">
         <f>IF($V242="","",INDEX($R$2:$R$401,$V242))</f>
         <v/>
       </c>
@@ -18342,7 +18441,7 @@
       </c>
     </row>
     <row r="243" ht="22.5" customHeight="1">
-      <c r="A243" s="25">
+      <c r="A243" s="78">
         <f>IF($V243="","",INDEX($R$2:$R$401,$V243))</f>
         <v/>
       </c>
@@ -18386,7 +18485,7 @@
       </c>
     </row>
     <row r="244" ht="22.5" customHeight="1">
-      <c r="A244" s="35">
+      <c r="A244" s="85">
         <f>IF($V244="","",INDEX($R$2:$R$401,$V244))</f>
         <v/>
       </c>
@@ -18430,7 +18529,7 @@
       </c>
     </row>
     <row r="245" ht="22.5" customHeight="1">
-      <c r="A245" s="25">
+      <c r="A245" s="78">
         <f>IF($V245="","",INDEX($R$2:$R$401,$V245))</f>
         <v/>
       </c>
@@ -18474,7 +18573,7 @@
       </c>
     </row>
     <row r="246" ht="22.5" customHeight="1">
-      <c r="A246" s="35">
+      <c r="A246" s="85">
         <f>IF($V246="","",INDEX($R$2:$R$401,$V246))</f>
         <v/>
       </c>
@@ -18518,7 +18617,7 @@
       </c>
     </row>
     <row r="247" ht="22.5" customHeight="1">
-      <c r="A247" s="25">
+      <c r="A247" s="78">
         <f>IF($V247="","",INDEX($R$2:$R$401,$V247))</f>
         <v/>
       </c>
@@ -18562,7 +18661,7 @@
       </c>
     </row>
     <row r="248" ht="22.5" customHeight="1">
-      <c r="A248" s="35">
+      <c r="A248" s="85">
         <f>IF($V248="","",INDEX($R$2:$R$401,$V248))</f>
         <v/>
       </c>
@@ -18606,7 +18705,7 @@
       </c>
     </row>
     <row r="249" ht="22.5" customHeight="1">
-      <c r="A249" s="25">
+      <c r="A249" s="78">
         <f>IF($V249="","",INDEX($R$2:$R$401,$V249))</f>
         <v/>
       </c>
@@ -18650,7 +18749,7 @@
       </c>
     </row>
     <row r="250" ht="22.5" customHeight="1">
-      <c r="A250" s="35">
+      <c r="A250" s="85">
         <f>IF($V250="","",INDEX($R$2:$R$401,$V250))</f>
         <v/>
       </c>
@@ -18694,7 +18793,7 @@
       </c>
     </row>
     <row r="251" ht="22.5" customHeight="1">
-      <c r="A251" s="25">
+      <c r="A251" s="78">
         <f>IF($V251="","",INDEX($R$2:$R$401,$V251))</f>
         <v/>
       </c>
@@ -18738,7 +18837,7 @@
       </c>
     </row>
     <row r="252" ht="22.5" customHeight="1">
-      <c r="A252" s="35">
+      <c r="A252" s="85">
         <f>IF($V252="","",INDEX($R$2:$R$401,$V252))</f>
         <v/>
       </c>
@@ -18782,7 +18881,7 @@
       </c>
     </row>
     <row r="253" ht="22.5" customHeight="1">
-      <c r="A253" s="25">
+      <c r="A253" s="78">
         <f>IF($V253="","",INDEX($R$2:$R$401,$V253))</f>
         <v/>
       </c>
@@ -18826,7 +18925,7 @@
       </c>
     </row>
     <row r="254" ht="22.5" customHeight="1">
-      <c r="A254" s="35">
+      <c r="A254" s="85">
         <f>IF($V254="","",INDEX($R$2:$R$401,$V254))</f>
         <v/>
       </c>
@@ -18870,7 +18969,7 @@
       </c>
     </row>
     <row r="255" ht="22.5" customHeight="1">
-      <c r="A255" s="25">
+      <c r="A255" s="78">
         <f>IF($V255="","",INDEX($R$2:$R$401,$V255))</f>
         <v/>
       </c>
@@ -18914,7 +19013,7 @@
       </c>
     </row>
     <row r="256" ht="22.5" customHeight="1">
-      <c r="A256" s="35">
+      <c r="A256" s="85">
         <f>IF($V256="","",INDEX($R$2:$R$401,$V256))</f>
         <v/>
       </c>
@@ -18958,7 +19057,7 @@
       </c>
     </row>
     <row r="257" ht="22.5" customHeight="1">
-      <c r="A257" s="25">
+      <c r="A257" s="78">
         <f>IF($V257="","",INDEX($R$2:$R$401,$V257))</f>
         <v/>
       </c>
@@ -19002,7 +19101,7 @@
       </c>
     </row>
     <row r="258" ht="22.5" customHeight="1">
-      <c r="A258" s="35">
+      <c r="A258" s="85">
         <f>IF($V258="","",INDEX($R$2:$R$401,$V258))</f>
         <v/>
       </c>
@@ -19046,7 +19145,7 @@
       </c>
     </row>
     <row r="259" ht="22.5" customHeight="1">
-      <c r="A259" s="25">
+      <c r="A259" s="78">
         <f>IF($V259="","",INDEX($R$2:$R$401,$V259))</f>
         <v/>
       </c>
@@ -19090,7 +19189,7 @@
       </c>
     </row>
     <row r="260" ht="22.5" customHeight="1">
-      <c r="A260" s="35">
+      <c r="A260" s="85">
         <f>IF($V260="","",INDEX($R$2:$R$401,$V260))</f>
         <v/>
       </c>
@@ -19134,7 +19233,7 @@
       </c>
     </row>
     <row r="261" ht="22.5" customHeight="1">
-      <c r="A261" s="25">
+      <c r="A261" s="78">
         <f>IF($V261="","",INDEX($R$2:$R$401,$V261))</f>
         <v/>
       </c>
@@ -19178,7 +19277,7 @@
       </c>
     </row>
     <row r="262" ht="22.5" customHeight="1">
-      <c r="A262" s="35">
+      <c r="A262" s="85">
         <f>IF($V262="","",INDEX($R$2:$R$401,$V262))</f>
         <v/>
       </c>
@@ -19222,7 +19321,7 @@
       </c>
     </row>
     <row r="263" ht="22.5" customHeight="1">
-      <c r="A263" s="25">
+      <c r="A263" s="78">
         <f>IF($V263="","",INDEX($R$2:$R$401,$V263))</f>
         <v/>
       </c>
@@ -19266,7 +19365,7 @@
       </c>
     </row>
     <row r="264" ht="22.5" customHeight="1">
-      <c r="A264" s="35">
+      <c r="A264" s="85">
         <f>IF($V264="","",INDEX($R$2:$R$401,$V264))</f>
         <v/>
       </c>
@@ -19310,7 +19409,7 @@
       </c>
     </row>
     <row r="265" ht="22.5" customHeight="1">
-      <c r="A265" s="25">
+      <c r="A265" s="78">
         <f>IF($V265="","",INDEX($R$2:$R$401,$V265))</f>
         <v/>
       </c>
@@ -19354,7 +19453,7 @@
       </c>
     </row>
     <row r="266" ht="22.5" customHeight="1">
-      <c r="A266" s="35">
+      <c r="A266" s="85">
         <f>IF($V266="","",INDEX($R$2:$R$401,$V266))</f>
         <v/>
       </c>
@@ -19398,7 +19497,7 @@
       </c>
     </row>
     <row r="267" ht="22.5" customHeight="1">
-      <c r="A267" s="25">
+      <c r="A267" s="78">
         <f>IF($V267="","",INDEX($R$2:$R$401,$V267))</f>
         <v/>
       </c>
@@ -19442,7 +19541,7 @@
       </c>
     </row>
     <row r="268" ht="22.5" customHeight="1">
-      <c r="A268" s="35">
+      <c r="A268" s="85">
         <f>IF($V268="","",INDEX($R$2:$R$401,$V268))</f>
         <v/>
       </c>
@@ -19486,7 +19585,7 @@
       </c>
     </row>
     <row r="269" ht="22.5" customHeight="1">
-      <c r="A269" s="25">
+      <c r="A269" s="78">
         <f>IF($V269="","",INDEX($R$2:$R$401,$V269))</f>
         <v/>
       </c>
@@ -19530,7 +19629,7 @@
       </c>
     </row>
     <row r="270" ht="22.5" customHeight="1">
-      <c r="A270" s="35">
+      <c r="A270" s="85">
         <f>IF($V270="","",INDEX($R$2:$R$401,$V270))</f>
         <v/>
       </c>
@@ -19574,7 +19673,7 @@
       </c>
     </row>
     <row r="271" ht="22.5" customHeight="1">
-      <c r="A271" s="25">
+      <c r="A271" s="78">
         <f>IF($V271="","",INDEX($R$2:$R$401,$V271))</f>
         <v/>
       </c>
@@ -19618,7 +19717,7 @@
       </c>
     </row>
     <row r="272" ht="22.5" customHeight="1">
-      <c r="A272" s="35">
+      <c r="A272" s="85">
         <f>IF($V272="","",INDEX($R$2:$R$401,$V272))</f>
         <v/>
       </c>
@@ -19662,7 +19761,7 @@
       </c>
     </row>
     <row r="273" ht="22.5" customHeight="1">
-      <c r="A273" s="25">
+      <c r="A273" s="78">
         <f>IF($V273="","",INDEX($R$2:$R$401,$V273))</f>
         <v/>
       </c>
@@ -19706,7 +19805,7 @@
       </c>
     </row>
     <row r="274" ht="22.5" customHeight="1">
-      <c r="A274" s="35">
+      <c r="A274" s="85">
         <f>IF($V274="","",INDEX($R$2:$R$401,$V274))</f>
         <v/>
       </c>
@@ -19750,7 +19849,7 @@
       </c>
     </row>
     <row r="275" ht="22.5" customHeight="1">
-      <c r="A275" s="25">
+      <c r="A275" s="78">
         <f>IF($V275="","",INDEX($R$2:$R$401,$V275))</f>
         <v/>
       </c>
@@ -19794,7 +19893,7 @@
       </c>
     </row>
     <row r="276" ht="22.5" customHeight="1">
-      <c r="A276" s="35">
+      <c r="A276" s="85">
         <f>IF($V276="","",INDEX($R$2:$R$401,$V276))</f>
         <v/>
       </c>
@@ -19838,7 +19937,7 @@
       </c>
     </row>
     <row r="277" ht="22.5" customHeight="1">
-      <c r="A277" s="25">
+      <c r="A277" s="78">
         <f>IF($V277="","",INDEX($R$2:$R$401,$V277))</f>
         <v/>
       </c>
@@ -19882,7 +19981,7 @@
       </c>
     </row>
     <row r="278" ht="22.5" customHeight="1">
-      <c r="A278" s="35">
+      <c r="A278" s="85">
         <f>IF($V278="","",INDEX($R$2:$R$401,$V278))</f>
         <v/>
       </c>
@@ -19926,7 +20025,7 @@
       </c>
     </row>
     <row r="279" ht="22.5" customHeight="1">
-      <c r="A279" s="25">
+      <c r="A279" s="78">
         <f>IF($V279="","",INDEX($R$2:$R$401,$V279))</f>
         <v/>
       </c>
@@ -19970,7 +20069,7 @@
       </c>
     </row>
     <row r="280" ht="22.5" customHeight="1">
-      <c r="A280" s="35">
+      <c r="A280" s="85">
         <f>IF($V280="","",INDEX($R$2:$R$401,$V280))</f>
         <v/>
       </c>
@@ -20014,7 +20113,7 @@
       </c>
     </row>
     <row r="281" ht="22.5" customHeight="1">
-      <c r="A281" s="25">
+      <c r="A281" s="78">
         <f>IF($V281="","",INDEX($R$2:$R$401,$V281))</f>
         <v/>
       </c>
@@ -20058,7 +20157,7 @@
       </c>
     </row>
     <row r="282" ht="22.5" customHeight="1">
-      <c r="A282" s="35">
+      <c r="A282" s="85">
         <f>IF($V282="","",INDEX($R$2:$R$401,$V282))</f>
         <v/>
       </c>
@@ -20102,7 +20201,7 @@
       </c>
     </row>
     <row r="283" ht="22.5" customHeight="1">
-      <c r="A283" s="25">
+      <c r="A283" s="78">
         <f>IF($V283="","",INDEX($R$2:$R$401,$V283))</f>
         <v/>
       </c>
@@ -20146,7 +20245,7 @@
       </c>
     </row>
     <row r="284" ht="22.5" customHeight="1">
-      <c r="A284" s="35">
+      <c r="A284" s="85">
         <f>IF($V284="","",INDEX($R$2:$R$401,$V284))</f>
         <v/>
       </c>
@@ -20190,7 +20289,7 @@
       </c>
     </row>
     <row r="285" ht="22.5" customHeight="1">
-      <c r="A285" s="25">
+      <c r="A285" s="78">
         <f>IF($V285="","",INDEX($R$2:$R$401,$V285))</f>
         <v/>
       </c>
@@ -20234,7 +20333,7 @@
       </c>
     </row>
     <row r="286" ht="22.5" customHeight="1">
-      <c r="A286" s="35">
+      <c r="A286" s="85">
         <f>IF($V286="","",INDEX($R$2:$R$401,$V286))</f>
         <v/>
       </c>
@@ -20278,7 +20377,7 @@
       </c>
     </row>
     <row r="287" ht="22.5" customHeight="1">
-      <c r="A287" s="25">
+      <c r="A287" s="78">
         <f>IF($V287="","",INDEX($R$2:$R$401,$V287))</f>
         <v/>
       </c>
@@ -20322,7 +20421,7 @@
       </c>
     </row>
     <row r="288" ht="22.5" customHeight="1">
-      <c r="A288" s="35">
+      <c r="A288" s="85">
         <f>IF($V288="","",INDEX($R$2:$R$401,$V288))</f>
         <v/>
       </c>
@@ -20366,7 +20465,7 @@
       </c>
     </row>
     <row r="289" ht="22.5" customHeight="1">
-      <c r="A289" s="25">
+      <c r="A289" s="78">
         <f>IF($V289="","",INDEX($R$2:$R$401,$V289))</f>
         <v/>
       </c>
@@ -20410,7 +20509,7 @@
       </c>
     </row>
     <row r="290" ht="22.5" customHeight="1">
-      <c r="A290" s="35">
+      <c r="A290" s="85">
         <f>IF($V290="","",INDEX($R$2:$R$401,$V290))</f>
         <v/>
       </c>
@@ -20454,7 +20553,7 @@
       </c>
     </row>
     <row r="291" ht="22.5" customHeight="1">
-      <c r="A291" s="25">
+      <c r="A291" s="78">
         <f>IF($V291="","",INDEX($R$2:$R$401,$V291))</f>
         <v/>
       </c>
@@ -20498,7 +20597,7 @@
       </c>
     </row>
     <row r="292" ht="22.5" customHeight="1">
-      <c r="A292" s="35">
+      <c r="A292" s="85">
         <f>IF($V292="","",INDEX($R$2:$R$401,$V292))</f>
         <v/>
       </c>
@@ -20542,7 +20641,7 @@
       </c>
     </row>
     <row r="293" ht="22.5" customHeight="1">
-      <c r="A293" s="25">
+      <c r="A293" s="78">
         <f>IF($V293="","",INDEX($R$2:$R$401,$V293))</f>
         <v/>
       </c>
@@ -20586,7 +20685,7 @@
       </c>
     </row>
     <row r="294" ht="22.5" customHeight="1">
-      <c r="A294" s="35">
+      <c r="A294" s="85">
         <f>IF($V294="","",INDEX($R$2:$R$401,$V294))</f>
         <v/>
       </c>
@@ -20630,7 +20729,7 @@
       </c>
     </row>
     <row r="295" ht="22.5" customHeight="1">
-      <c r="A295" s="25">
+      <c r="A295" s="78">
         <f>IF($V295="","",INDEX($R$2:$R$401,$V295))</f>
         <v/>
       </c>
@@ -20674,7 +20773,7 @@
       </c>
     </row>
     <row r="296" ht="22.5" customHeight="1">
-      <c r="A296" s="35">
+      <c r="A296" s="85">
         <f>IF($V296="","",INDEX($R$2:$R$401,$V296))</f>
         <v/>
       </c>
@@ -20718,7 +20817,7 @@
       </c>
     </row>
     <row r="297" ht="22.5" customHeight="1">
-      <c r="A297" s="25">
+      <c r="A297" s="78">
         <f>IF($V297="","",INDEX($R$2:$R$401,$V297))</f>
         <v/>
       </c>
@@ -20762,7 +20861,7 @@
       </c>
     </row>
     <row r="298" ht="22.5" customHeight="1">
-      <c r="A298" s="35">
+      <c r="A298" s="85">
         <f>IF($V298="","",INDEX($R$2:$R$401,$V298))</f>
         <v/>
       </c>
@@ -20806,7 +20905,7 @@
       </c>
     </row>
     <row r="299" ht="22.5" customHeight="1">
-      <c r="A299" s="25">
+      <c r="A299" s="78">
         <f>IF($V299="","",INDEX($R$2:$R$401,$V299))</f>
         <v/>
       </c>
@@ -20850,7 +20949,7 @@
       </c>
     </row>
     <row r="300" ht="22.5" customHeight="1">
-      <c r="A300" s="35">
+      <c r="A300" s="85">
         <f>IF($V300="","",INDEX($R$2:$R$401,$V300))</f>
         <v/>
       </c>
@@ -20894,7 +20993,7 @@
       </c>
     </row>
     <row r="301" ht="22.5" customHeight="1">
-      <c r="A301" s="25">
+      <c r="A301" s="78">
         <f>IF($V301="","",INDEX($R$2:$R$401,$V301))</f>
         <v/>
       </c>
@@ -20938,7 +21037,7 @@
       </c>
     </row>
     <row r="302" ht="22.5" customHeight="1">
-      <c r="A302" s="35">
+      <c r="A302" s="85">
         <f>IF($V302="","",INDEX($R$2:$R$401,$V302))</f>
         <v/>
       </c>
@@ -20982,7 +21081,7 @@
       </c>
     </row>
     <row r="303" ht="22.5" customHeight="1">
-      <c r="A303" s="25">
+      <c r="A303" s="78">
         <f>IF($V303="","",INDEX($R$2:$R$401,$V303))</f>
         <v/>
       </c>
@@ -21026,7 +21125,7 @@
       </c>
     </row>
     <row r="304" ht="22.5" customHeight="1">
-      <c r="A304" s="35">
+      <c r="A304" s="85">
         <f>IF($V304="","",INDEX($R$2:$R$401,$V304))</f>
         <v/>
       </c>
@@ -21070,7 +21169,7 @@
       </c>
     </row>
     <row r="305" ht="22.5" customHeight="1">
-      <c r="A305" s="25">
+      <c r="A305" s="78">
         <f>IF($V305="","",INDEX($R$2:$R$401,$V305))</f>
         <v/>
       </c>
@@ -21114,7 +21213,7 @@
       </c>
     </row>
     <row r="306" ht="22.5" customHeight="1">
-      <c r="A306" s="35">
+      <c r="A306" s="85">
         <f>IF($V306="","",INDEX($R$2:$R$401,$V306))</f>
         <v/>
       </c>
@@ -21158,7 +21257,7 @@
       </c>
     </row>
     <row r="307" ht="22.5" customHeight="1">
-      <c r="A307" s="25">
+      <c r="A307" s="78">
         <f>IF($V307="","",INDEX($R$2:$R$401,$V307))</f>
         <v/>
       </c>
@@ -21202,7 +21301,7 @@
       </c>
     </row>
     <row r="308" ht="22.5" customHeight="1">
-      <c r="A308" s="35">
+      <c r="A308" s="85">
         <f>IF($V308="","",INDEX($R$2:$R$401,$V308))</f>
         <v/>
       </c>
@@ -21246,7 +21345,7 @@
       </c>
     </row>
     <row r="309" ht="22.5" customHeight="1">
-      <c r="A309" s="25">
+      <c r="A309" s="78">
         <f>IF($V309="","",INDEX($R$2:$R$401,$V309))</f>
         <v/>
       </c>
@@ -21290,7 +21389,7 @@
       </c>
     </row>
     <row r="310" ht="22.5" customHeight="1">
-      <c r="A310" s="35">
+      <c r="A310" s="85">
         <f>IF($V310="","",INDEX($R$2:$R$401,$V310))</f>
         <v/>
       </c>
@@ -21334,7 +21433,7 @@
       </c>
     </row>
     <row r="311" ht="22.5" customHeight="1">
-      <c r="A311" s="25">
+      <c r="A311" s="78">
         <f>IF($V311="","",INDEX($R$2:$R$401,$V311))</f>
         <v/>
       </c>
@@ -21378,7 +21477,7 @@
       </c>
     </row>
     <row r="312" ht="22.5" customHeight="1">
-      <c r="A312" s="35">
+      <c r="A312" s="85">
         <f>IF($V312="","",INDEX($R$2:$R$401,$V312))</f>
         <v/>
       </c>
@@ -21422,7 +21521,7 @@
       </c>
     </row>
     <row r="313" ht="22.5" customHeight="1">
-      <c r="A313" s="25">
+      <c r="A313" s="78">
         <f>IF($V313="","",INDEX($R$2:$R$401,$V313))</f>
         <v/>
       </c>
@@ -21466,7 +21565,7 @@
       </c>
     </row>
     <row r="314" ht="22.5" customHeight="1">
-      <c r="A314" s="35">
+      <c r="A314" s="85">
         <f>IF($V314="","",INDEX($R$2:$R$401,$V314))</f>
         <v/>
       </c>
@@ -21510,7 +21609,7 @@
       </c>
     </row>
     <row r="315" ht="22.5" customHeight="1">
-      <c r="A315" s="25">
+      <c r="A315" s="78">
         <f>IF($V315="","",INDEX($R$2:$R$401,$V315))</f>
         <v/>
       </c>
@@ -21554,7 +21653,7 @@
       </c>
     </row>
     <row r="316" ht="22.5" customHeight="1">
-      <c r="A316" s="35">
+      <c r="A316" s="85">
         <f>IF($V316="","",INDEX($R$2:$R$401,$V316))</f>
         <v/>
       </c>
@@ -21598,7 +21697,7 @@
       </c>
     </row>
     <row r="317" ht="22.5" customHeight="1">
-      <c r="A317" s="25">
+      <c r="A317" s="78">
         <f>IF($V317="","",INDEX($R$2:$R$401,$V317))</f>
         <v/>
       </c>
@@ -21642,7 +21741,7 @@
       </c>
     </row>
     <row r="318" ht="22.5" customHeight="1">
-      <c r="A318" s="35">
+      <c r="A318" s="85">
         <f>IF($V318="","",INDEX($R$2:$R$401,$V318))</f>
         <v/>
       </c>
@@ -21686,7 +21785,7 @@
       </c>
     </row>
     <row r="319" ht="22.5" customHeight="1">
-      <c r="A319" s="25">
+      <c r="A319" s="78">
         <f>IF($V319="","",INDEX($R$2:$R$401,$V319))</f>
         <v/>
       </c>
@@ -21730,7 +21829,7 @@
       </c>
     </row>
     <row r="320" ht="22.5" customHeight="1">
-      <c r="A320" s="35">
+      <c r="A320" s="85">
         <f>IF($V320="","",INDEX($R$2:$R$401,$V320))</f>
         <v/>
       </c>
@@ -21774,7 +21873,7 @@
       </c>
     </row>
     <row r="321" ht="22.5" customHeight="1">
-      <c r="A321" s="25">
+      <c r="A321" s="78">
         <f>IF($V321="","",INDEX($R$2:$R$401,$V321))</f>
         <v/>
       </c>
@@ -21818,7 +21917,7 @@
       </c>
     </row>
     <row r="322" ht="22.5" customHeight="1">
-      <c r="A322" s="35">
+      <c r="A322" s="85">
         <f>IF($V322="","",INDEX($R$2:$R$401,$V322))</f>
         <v/>
       </c>
@@ -21862,7 +21961,7 @@
       </c>
     </row>
     <row r="323" ht="22.5" customHeight="1">
-      <c r="A323" s="25">
+      <c r="A323" s="78">
         <f>IF($V323="","",INDEX($R$2:$R$401,$V323))</f>
         <v/>
       </c>
@@ -21906,7 +22005,7 @@
       </c>
     </row>
     <row r="324" ht="22.5" customHeight="1">
-      <c r="A324" s="35">
+      <c r="A324" s="85">
         <f>IF($V324="","",INDEX($R$2:$R$401,$V324))</f>
         <v/>
       </c>
@@ -21950,7 +22049,7 @@
       </c>
     </row>
     <row r="325" ht="22.5" customHeight="1">
-      <c r="A325" s="25">
+      <c r="A325" s="78">
         <f>IF($V325="","",INDEX($R$2:$R$401,$V325))</f>
         <v/>
       </c>
@@ -21994,7 +22093,7 @@
       </c>
     </row>
     <row r="326" ht="22.5" customHeight="1">
-      <c r="A326" s="35">
+      <c r="A326" s="85">
         <f>IF($V326="","",INDEX($R$2:$R$401,$V326))</f>
         <v/>
       </c>
@@ -22038,7 +22137,7 @@
       </c>
     </row>
     <row r="327" ht="22.5" customHeight="1">
-      <c r="A327" s="25">
+      <c r="A327" s="78">
         <f>IF($V327="","",INDEX($R$2:$R$401,$V327))</f>
         <v/>
       </c>
@@ -22082,7 +22181,7 @@
       </c>
     </row>
     <row r="328" ht="22.5" customHeight="1">
-      <c r="A328" s="35">
+      <c r="A328" s="85">
         <f>IF($V328="","",INDEX($R$2:$R$401,$V328))</f>
         <v/>
       </c>
@@ -22126,7 +22225,7 @@
       </c>
     </row>
     <row r="329" ht="22.5" customHeight="1">
-      <c r="A329" s="25">
+      <c r="A329" s="78">
         <f>IF($V329="","",INDEX($R$2:$R$401,$V329))</f>
         <v/>
       </c>
@@ -22170,7 +22269,7 @@
       </c>
     </row>
     <row r="330" ht="22.5" customHeight="1">
-      <c r="A330" s="35">
+      <c r="A330" s="85">
         <f>IF($V330="","",INDEX($R$2:$R$401,$V330))</f>
         <v/>
       </c>
@@ -22214,7 +22313,7 @@
       </c>
     </row>
     <row r="331" ht="22.5" customHeight="1">
-      <c r="A331" s="25">
+      <c r="A331" s="78">
         <f>IF($V331="","",INDEX($R$2:$R$401,$V331))</f>
         <v/>
       </c>
@@ -22258,7 +22357,7 @@
       </c>
     </row>
     <row r="332" ht="22.5" customHeight="1">
-      <c r="A332" s="35">
+      <c r="A332" s="85">
         <f>IF($V332="","",INDEX($R$2:$R$401,$V332))</f>
         <v/>
       </c>
@@ -22302,7 +22401,7 @@
       </c>
     </row>
     <row r="333" ht="22.5" customHeight="1">
-      <c r="A333" s="25">
+      <c r="A333" s="78">
         <f>IF($V333="","",INDEX($R$2:$R$401,$V333))</f>
         <v/>
       </c>
@@ -22346,7 +22445,7 @@
       </c>
     </row>
     <row r="334" ht="22.5" customHeight="1">
-      <c r="A334" s="35">
+      <c r="A334" s="85">
         <f>IF($V334="","",INDEX($R$2:$R$401,$V334))</f>
         <v/>
       </c>
@@ -22390,7 +22489,7 @@
       </c>
     </row>
     <row r="335" ht="22.5" customHeight="1">
-      <c r="A335" s="25">
+      <c r="A335" s="78">
         <f>IF($V335="","",INDEX($R$2:$R$401,$V335))</f>
         <v/>
       </c>
@@ -22434,7 +22533,7 @@
       </c>
     </row>
     <row r="336" ht="22.5" customHeight="1">
-      <c r="A336" s="35">
+      <c r="A336" s="85">
         <f>IF($V336="","",INDEX($R$2:$R$401,$V336))</f>
         <v/>
       </c>
@@ -22478,7 +22577,7 @@
       </c>
     </row>
     <row r="337" ht="22.5" customHeight="1">
-      <c r="A337" s="25">
+      <c r="A337" s="78">
         <f>IF($V337="","",INDEX($R$2:$R$401,$V337))</f>
         <v/>
       </c>
@@ -22522,7 +22621,7 @@
       </c>
     </row>
     <row r="338" ht="22.5" customHeight="1">
-      <c r="A338" s="35">
+      <c r="A338" s="85">
         <f>IF($V338="","",INDEX($R$2:$R$401,$V338))</f>
         <v/>
       </c>
@@ -22566,7 +22665,7 @@
       </c>
     </row>
     <row r="339" ht="22.5" customHeight="1">
-      <c r="A339" s="25">
+      <c r="A339" s="78">
         <f>IF($V339="","",INDEX($R$2:$R$401,$V339))</f>
         <v/>
       </c>
@@ -22610,7 +22709,7 @@
       </c>
     </row>
     <row r="340" ht="22.5" customHeight="1">
-      <c r="A340" s="35">
+      <c r="A340" s="85">
         <f>IF($V340="","",INDEX($R$2:$R$401,$V340))</f>
         <v/>
       </c>
@@ -22654,7 +22753,7 @@
       </c>
     </row>
     <row r="341" ht="22.5" customHeight="1">
-      <c r="A341" s="25">
+      <c r="A341" s="78">
         <f>IF($V341="","",INDEX($R$2:$R$401,$V341))</f>
         <v/>
       </c>
@@ -22698,7 +22797,7 @@
       </c>
     </row>
     <row r="342" ht="22.5" customHeight="1">
-      <c r="A342" s="35">
+      <c r="A342" s="85">
         <f>IF($V342="","",INDEX($R$2:$R$401,$V342))</f>
         <v/>
       </c>
@@ -22742,7 +22841,7 @@
       </c>
     </row>
     <row r="343" ht="22.5" customHeight="1">
-      <c r="A343" s="25">
+      <c r="A343" s="78">
         <f>IF($V343="","",INDEX($R$2:$R$401,$V343))</f>
         <v/>
       </c>
@@ -22786,7 +22885,7 @@
       </c>
     </row>
     <row r="344" ht="22.5" customHeight="1">
-      <c r="A344" s="35">
+      <c r="A344" s="85">
         <f>IF($V344="","",INDEX($R$2:$R$401,$V344))</f>
         <v/>
       </c>
@@ -22830,7 +22929,7 @@
       </c>
     </row>
     <row r="345" ht="22.5" customHeight="1">
-      <c r="A345" s="25">
+      <c r="A345" s="78">
         <f>IF($V345="","",INDEX($R$2:$R$401,$V345))</f>
         <v/>
       </c>
@@ -22874,7 +22973,7 @@
       </c>
     </row>
     <row r="346" ht="22.5" customHeight="1">
-      <c r="A346" s="35">
+      <c r="A346" s="85">
         <f>IF($V346="","",INDEX($R$2:$R$401,$V346))</f>
         <v/>
       </c>
@@ -22918,7 +23017,7 @@
       </c>
     </row>
     <row r="347" ht="22.5" customHeight="1">
-      <c r="A347" s="25">
+      <c r="A347" s="78">
         <f>IF($V347="","",INDEX($R$2:$R$401,$V347))</f>
         <v/>
       </c>
@@ -22962,7 +23061,7 @@
       </c>
     </row>
     <row r="348" ht="22.5" customHeight="1">
-      <c r="A348" s="35">
+      <c r="A348" s="85">
         <f>IF($V348="","",INDEX($R$2:$R$401,$V348))</f>
         <v/>
       </c>
@@ -23006,7 +23105,7 @@
       </c>
     </row>
     <row r="349" ht="22.5" customHeight="1">
-      <c r="A349" s="25">
+      <c r="A349" s="78">
         <f>IF($V349="","",INDEX($R$2:$R$401,$V349))</f>
         <v/>
       </c>
@@ -23050,7 +23149,7 @@
       </c>
     </row>
     <row r="350" ht="22.5" customHeight="1">
-      <c r="A350" s="35">
+      <c r="A350" s="85">
         <f>IF($V350="","",INDEX($R$2:$R$401,$V350))</f>
         <v/>
       </c>
@@ -23094,7 +23193,7 @@
       </c>
     </row>
     <row r="351" ht="22.5" customHeight="1">
-      <c r="A351" s="25">
+      <c r="A351" s="78">
         <f>IF($V351="","",INDEX($R$2:$R$401,$V351))</f>
         <v/>
       </c>
@@ -23138,7 +23237,7 @@
       </c>
     </row>
     <row r="352" ht="22.5" customHeight="1">
-      <c r="A352" s="35">
+      <c r="A352" s="85">
         <f>IF($V352="","",INDEX($R$2:$R$401,$V352))</f>
         <v/>
       </c>
@@ -23182,7 +23281,7 @@
       </c>
     </row>
     <row r="353" ht="22.5" customHeight="1">
-      <c r="A353" s="25">
+      <c r="A353" s="78">
         <f>IF($V353="","",INDEX($R$2:$R$401,$V353))</f>
         <v/>
       </c>
@@ -23226,7 +23325,7 @@
       </c>
     </row>
     <row r="354" ht="22.5" customHeight="1">
-      <c r="A354" s="35">
+      <c r="A354" s="85">
         <f>IF($V354="","",INDEX($R$2:$R$401,$V354))</f>
         <v/>
       </c>
@@ -23270,7 +23369,7 @@
       </c>
     </row>
     <row r="355" ht="22.5" customHeight="1">
-      <c r="A355" s="25">
+      <c r="A355" s="78">
         <f>IF($V355="","",INDEX($R$2:$R$401,$V355))</f>
         <v/>
       </c>
@@ -23314,7 +23413,7 @@
       </c>
     </row>
     <row r="356" ht="22.5" customHeight="1">
-      <c r="A356" s="35">
+      <c r="A356" s="85">
         <f>IF($V356="","",INDEX($R$2:$R$401,$V356))</f>
         <v/>
       </c>
@@ -23358,7 +23457,7 @@
       </c>
     </row>
     <row r="357" ht="22.5" customHeight="1">
-      <c r="A357" s="25">
+      <c r="A357" s="78">
         <f>IF($V357="","",INDEX($R$2:$R$401,$V357))</f>
         <v/>
       </c>
@@ -23402,7 +23501,7 @@
       </c>
     </row>
     <row r="358" ht="22.5" customHeight="1">
-      <c r="A358" s="35">
+      <c r="A358" s="85">
         <f>IF($V358="","",INDEX($R$2:$R$401,$V358))</f>
         <v/>
       </c>
@@ -23446,7 +23545,7 @@
       </c>
     </row>
     <row r="359" ht="22.5" customHeight="1">
-      <c r="A359" s="25">
+      <c r="A359" s="78">
         <f>IF($V359="","",INDEX($R$2:$R$401,$V359))</f>
         <v/>
       </c>
@@ -23490,7 +23589,7 @@
       </c>
     </row>
     <row r="360" ht="22.5" customHeight="1">
-      <c r="A360" s="35">
+      <c r="A360" s="85">
         <f>IF($V360="","",INDEX($R$2:$R$401,$V360))</f>
         <v/>
       </c>
@@ -23534,7 +23633,7 @@
       </c>
     </row>
     <row r="361" ht="22.5" customHeight="1">
-      <c r="A361" s="25">
+      <c r="A361" s="78">
         <f>IF($V361="","",INDEX($R$2:$R$401,$V361))</f>
         <v/>
       </c>
@@ -23578,7 +23677,7 @@
       </c>
     </row>
     <row r="362" ht="22.5" customHeight="1">
-      <c r="A362" s="35">
+      <c r="A362" s="85">
         <f>IF($V362="","",INDEX($R$2:$R$401,$V362))</f>
         <v/>
       </c>
@@ -23622,7 +23721,7 @@
       </c>
     </row>
     <row r="363" ht="22.5" customHeight="1">
-      <c r="A363" s="25">
+      <c r="A363" s="78">
         <f>IF($V363="","",INDEX($R$2:$R$401,$V363))</f>
         <v/>
       </c>
@@ -23666,7 +23765,7 @@
       </c>
     </row>
     <row r="364" ht="22.5" customHeight="1">
-      <c r="A364" s="35">
+      <c r="A364" s="85">
         <f>IF($V364="","",INDEX($R$2:$R$401,$V364))</f>
         <v/>
       </c>
@@ -23710,7 +23809,7 @@
       </c>
     </row>
     <row r="365" ht="22.5" customHeight="1">
-      <c r="A365" s="25">
+      <c r="A365" s="78">
         <f>IF($V365="","",INDEX($R$2:$R$401,$V365))</f>
         <v/>
       </c>
@@ -23754,7 +23853,7 @@
       </c>
     </row>
     <row r="366" ht="22.5" customHeight="1">
-      <c r="A366" s="35">
+      <c r="A366" s="85">
         <f>IF($V366="","",INDEX($R$2:$R$401,$V366))</f>
         <v/>
       </c>
@@ -23798,7 +23897,7 @@
       </c>
     </row>
     <row r="367" ht="22.5" customHeight="1">
-      <c r="A367" s="25">
+      <c r="A367" s="78">
         <f>IF($V367="","",INDEX($R$2:$R$401,$V367))</f>
         <v/>
       </c>
@@ -23842,7 +23941,7 @@
       </c>
     </row>
     <row r="368" ht="22.5" customHeight="1">
-      <c r="A368" s="35">
+      <c r="A368" s="85">
         <f>IF($V368="","",INDEX($R$2:$R$401,$V368))</f>
         <v/>
       </c>
@@ -23886,7 +23985,7 @@
       </c>
     </row>
     <row r="369" ht="22.5" customHeight="1">
-      <c r="A369" s="25">
+      <c r="A369" s="78">
         <f>IF($V369="","",INDEX($R$2:$R$401,$V369))</f>
         <v/>
       </c>
@@ -23930,7 +24029,7 @@
       </c>
     </row>
     <row r="370" ht="22.5" customHeight="1">
-      <c r="A370" s="35">
+      <c r="A370" s="85">
         <f>IF($V370="","",INDEX($R$2:$R$401,$V370))</f>
         <v/>
       </c>
@@ -23974,7 +24073,7 @@
       </c>
     </row>
     <row r="371" ht="22.5" customHeight="1">
-      <c r="A371" s="25">
+      <c r="A371" s="78">
         <f>IF($V371="","",INDEX($R$2:$R$401,$V371))</f>
         <v/>
       </c>
@@ -24018,7 +24117,7 @@
       </c>
     </row>
     <row r="372" ht="22.5" customHeight="1">
-      <c r="A372" s="35">
+      <c r="A372" s="85">
         <f>IF($V372="","",INDEX($R$2:$R$401,$V372))</f>
         <v/>
       </c>
@@ -24062,7 +24161,7 @@
       </c>
     </row>
     <row r="373" ht="22.5" customHeight="1">
-      <c r="A373" s="25">
+      <c r="A373" s="78">
         <f>IF($V373="","",INDEX($R$2:$R$401,$V373))</f>
         <v/>
       </c>
@@ -24106,7 +24205,7 @@
       </c>
     </row>
     <row r="374" ht="22.5" customHeight="1">
-      <c r="A374" s="35">
+      <c r="A374" s="85">
         <f>IF($V374="","",INDEX($R$2:$R$401,$V374))</f>
         <v/>
       </c>
@@ -24150,7 +24249,7 @@
       </c>
     </row>
     <row r="375" ht="22.5" customHeight="1">
-      <c r="A375" s="25">
+      <c r="A375" s="78">
         <f>IF($V375="","",INDEX($R$2:$R$401,$V375))</f>
         <v/>
       </c>
@@ -24194,7 +24293,7 @@
       </c>
     </row>
     <row r="376" ht="22.5" customHeight="1">
-      <c r="A376" s="35">
+      <c r="A376" s="85">
         <f>IF($V376="","",INDEX($R$2:$R$401,$V376))</f>
         <v/>
       </c>
@@ -24238,7 +24337,7 @@
       </c>
     </row>
     <row r="377" ht="22.5" customHeight="1">
-      <c r="A377" s="25">
+      <c r="A377" s="78">
         <f>IF($V377="","",INDEX($R$2:$R$401,$V377))</f>
         <v/>
       </c>
@@ -24282,7 +24381,7 @@
       </c>
     </row>
     <row r="378" ht="22.5" customHeight="1">
-      <c r="A378" s="35">
+      <c r="A378" s="85">
         <f>IF($V378="","",INDEX($R$2:$R$401,$V378))</f>
         <v/>
       </c>
@@ -24326,7 +24425,7 @@
       </c>
     </row>
     <row r="379" ht="22.5" customHeight="1">
-      <c r="A379" s="25">
+      <c r="A379" s="78">
         <f>IF($V379="","",INDEX($R$2:$R$401,$V379))</f>
         <v/>
       </c>
@@ -24370,7 +24469,7 @@
       </c>
     </row>
     <row r="380" ht="22.5" customHeight="1">
-      <c r="A380" s="35">
+      <c r="A380" s="85">
         <f>IF($V380="","",INDEX($R$2:$R$401,$V380))</f>
         <v/>
       </c>
@@ -24414,7 +24513,7 @@
       </c>
     </row>
     <row r="381" ht="22.5" customHeight="1">
-      <c r="A381" s="25">
+      <c r="A381" s="78">
         <f>IF($V381="","",INDEX($R$2:$R$401,$V381))</f>
         <v/>
       </c>
@@ -24458,7 +24557,7 @@
       </c>
     </row>
     <row r="382" ht="22.5" customHeight="1">
-      <c r="A382" s="35">
+      <c r="A382" s="85">
         <f>IF($V382="","",INDEX($R$2:$R$401,$V382))</f>
         <v/>
       </c>
@@ -24502,7 +24601,7 @@
       </c>
     </row>
     <row r="383" ht="22.5" customHeight="1">
-      <c r="A383" s="25">
+      <c r="A383" s="78">
         <f>IF($V383="","",INDEX($R$2:$R$401,$V383))</f>
         <v/>
       </c>
@@ -24546,7 +24645,7 @@
       </c>
     </row>
     <row r="384" ht="22.5" customHeight="1">
-      <c r="A384" s="35">
+      <c r="A384" s="85">
         <f>IF($V384="","",INDEX($R$2:$R$401,$V384))</f>
         <v/>
       </c>
@@ -24590,7 +24689,7 @@
       </c>
     </row>
     <row r="385" ht="22.5" customHeight="1">
-      <c r="A385" s="25">
+      <c r="A385" s="78">
         <f>IF($V385="","",INDEX($R$2:$R$401,$V385))</f>
         <v/>
       </c>
@@ -24634,7 +24733,7 @@
       </c>
     </row>
     <row r="386" ht="22.5" customHeight="1">
-      <c r="A386" s="35">
+      <c r="A386" s="85">
         <f>IF($V386="","",INDEX($R$2:$R$401,$V386))</f>
         <v/>
       </c>
@@ -24678,7 +24777,7 @@
       </c>
     </row>
     <row r="387" ht="22.5" customHeight="1">
-      <c r="A387" s="25">
+      <c r="A387" s="78">
         <f>IF($V387="","",INDEX($R$2:$R$401,$V387))</f>
         <v/>
       </c>
@@ -24722,7 +24821,7 @@
       </c>
     </row>
     <row r="388" ht="22.5" customHeight="1">
-      <c r="A388" s="35">
+      <c r="A388" s="85">
         <f>IF($V388="","",INDEX($R$2:$R$401,$V388))</f>
         <v/>
       </c>
@@ -24766,7 +24865,7 @@
       </c>
     </row>
     <row r="389" ht="22.5" customHeight="1">
-      <c r="A389" s="25">
+      <c r="A389" s="78">
         <f>IF($V389="","",INDEX($R$2:$R$401,$V389))</f>
         <v/>
       </c>
@@ -24810,7 +24909,7 @@
       </c>
     </row>
     <row r="390" ht="22.5" customHeight="1">
-      <c r="A390" s="35">
+      <c r="A390" s="85">
         <f>IF($V390="","",INDEX($R$2:$R$401,$V390))</f>
         <v/>
       </c>
@@ -24854,7 +24953,7 @@
       </c>
     </row>
     <row r="391" ht="22.5" customHeight="1">
-      <c r="A391" s="25">
+      <c r="A391" s="78">
         <f>IF($V391="","",INDEX($R$2:$R$401,$V391))</f>
         <v/>
       </c>
@@ -24898,7 +24997,7 @@
       </c>
     </row>
     <row r="392" ht="22.5" customHeight="1">
-      <c r="A392" s="35">
+      <c r="A392" s="85">
         <f>IF($V392="","",INDEX($R$2:$R$401,$V392))</f>
         <v/>
       </c>
@@ -24942,7 +25041,7 @@
       </c>
     </row>
     <row r="393" ht="22.5" customHeight="1">
-      <c r="A393" s="25">
+      <c r="A393" s="78">
         <f>IF($V393="","",INDEX($R$2:$R$401,$V393))</f>
         <v/>
       </c>
@@ -24986,7 +25085,7 @@
       </c>
     </row>
     <row r="394" ht="22.5" customHeight="1">
-      <c r="A394" s="35">
+      <c r="A394" s="85">
         <f>IF($V394="","",INDEX($R$2:$R$401,$V394))</f>
         <v/>
       </c>
@@ -25030,7 +25129,7 @@
       </c>
     </row>
     <row r="395" ht="22.5" customHeight="1">
-      <c r="A395" s="25">
+      <c r="A395" s="78">
         <f>IF($V395="","",INDEX($R$2:$R$401,$V395))</f>
         <v/>
       </c>
@@ -25074,7 +25173,7 @@
       </c>
     </row>
     <row r="396" ht="22.5" customHeight="1">
-      <c r="A396" s="35">
+      <c r="A396" s="85">
         <f>IF($V396="","",INDEX($R$2:$R$401,$V396))</f>
         <v/>
       </c>
@@ -25118,7 +25217,7 @@
       </c>
     </row>
     <row r="397" ht="22.5" customHeight="1">
-      <c r="A397" s="25">
+      <c r="A397" s="78">
         <f>IF($V397="","",INDEX($R$2:$R$401,$V397))</f>
         <v/>
       </c>
@@ -25162,7 +25261,7 @@
       </c>
     </row>
     <row r="398" ht="22.5" customHeight="1">
-      <c r="A398" s="35">
+      <c r="A398" s="85">
         <f>IF($V398="","",INDEX($R$2:$R$401,$V398))</f>
         <v/>
       </c>
@@ -25206,7 +25305,7 @@
       </c>
     </row>
     <row r="399" ht="22.5" customHeight="1">
-      <c r="A399" s="25">
+      <c r="A399" s="78">
         <f>IF($V399="","",INDEX($R$2:$R$401,$V399))</f>
         <v/>
       </c>
@@ -25250,7 +25349,7 @@
       </c>
     </row>
     <row r="400" ht="22.5" customHeight="1">
-      <c r="A400" s="35">
+      <c r="A400" s="85">
         <f>IF($V400="","",INDEX($R$2:$R$401,$V400))</f>
         <v/>
       </c>
@@ -25294,7 +25393,7 @@
       </c>
     </row>
     <row r="401" ht="22.5" customHeight="1">
-      <c r="A401" s="25">
+      <c r="A401" s="78">
         <f>IF($V401="","",INDEX($R$2:$R$401,$V401))</f>
         <v/>
       </c>
@@ -25338,7 +25437,7 @@
       </c>
     </row>
     <row r="402" ht="22.5" customHeight="1">
-      <c r="A402" s="35">
+      <c r="A402" s="85">
         <f>IF($V402="","",INDEX($R$2:$R$401,$V402))</f>
         <v/>
       </c>
@@ -25364,7 +25463,7 @@
       </c>
     </row>
     <row r="403" ht="22.5" customHeight="1">
-      <c r="A403" s="25">
+      <c r="A403" s="78">
         <f>IF($V403="","",INDEX($R$2:$R$401,$V403))</f>
         <v/>
       </c>
@@ -25390,7 +25489,7 @@
       </c>
     </row>
     <row r="404" ht="22.5" customHeight="1">
-      <c r="A404" s="35">
+      <c r="A404" s="85">
         <f>IF($V404="","",INDEX($R$2:$R$401,$V404))</f>
         <v/>
       </c>
@@ -25416,7 +25515,7 @@
       </c>
     </row>
     <row r="405" ht="22.5" customHeight="1">
-      <c r="A405" s="25">
+      <c r="A405" s="78">
         <f>IF($V405="","",INDEX($R$2:$R$401,$V405))</f>
         <v/>
       </c>
@@ -25442,7 +25541,7 @@
       </c>
     </row>
     <row r="406" ht="22.5" customHeight="1">
-      <c r="A406" s="35">
+      <c r="A406" s="85">
         <f>IF($V406="","",INDEX($R$2:$R$401,$V406))</f>
         <v/>
       </c>
@@ -25468,7 +25567,7 @@
       </c>
     </row>
     <row r="407" ht="22.5" customHeight="1">
-      <c r="A407" s="25">
+      <c r="A407" s="78">
         <f>IF($V407="","",INDEX($R$2:$R$401,$V407))</f>
         <v/>
       </c>
@@ -25494,7 +25593,7 @@
       </c>
     </row>
     <row r="408" ht="22.5" customHeight="1">
-      <c r="A408" s="35">
+      <c r="A408" s="85">
         <f>IF($V408="","",INDEX($R$2:$R$401,$V408))</f>
         <v/>
       </c>
@@ -25520,7 +25619,7 @@
       </c>
     </row>
     <row r="409" ht="22.5" customHeight="1">
-      <c r="A409" s="25">
+      <c r="A409" s="78">
         <f>IF($V409="","",INDEX($R$2:$R$401,$V409))</f>
         <v/>
       </c>
@@ -25546,7 +25645,7 @@
       </c>
     </row>
     <row r="410" ht="22.5" customHeight="1">
-      <c r="A410" s="35">
+      <c r="A410" s="85">
         <f>IF($V410="","",INDEX($R$2:$R$401,$V410))</f>
         <v/>
       </c>
@@ -25572,7 +25671,7 @@
       </c>
     </row>
     <row r="411" ht="22.5" customHeight="1">
-      <c r="A411" s="25">
+      <c r="A411" s="78">
         <f>IF($V411="","",INDEX($R$2:$R$401,$V411))</f>
         <v/>
       </c>
@@ -25598,7 +25697,7 @@
       </c>
     </row>
     <row r="412" ht="22.5" customHeight="1">
-      <c r="A412" s="35">
+      <c r="A412" s="85">
         <f>IF($V412="","",INDEX($R$2:$R$401,$V412))</f>
         <v/>
       </c>
